--- a/daily_ethnicity_mix.xlsx
+++ b/daily_ethnicity_mix.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N366"/>
+  <dimension ref="A1:N367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9285,7 +9285,7 @@
         <v>17</v>
       </c>
       <c r="C193" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D193" t="n">
         <v>13</v>
@@ -9300,25 +9300,25 @@
         <v>0</v>
       </c>
       <c r="H193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I193" t="n">
         <v>11</v>
       </c>
       <c r="J193" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K193" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L193" t="n">
         <v>82</v>
       </c>
       <c r="M193" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="N193" t="n">
-        <v>69.5</v>
+        <v>67.09999999999999</v>
       </c>
     </row>
     <row r="194">
@@ -9420,13 +9420,13 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C196" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D196" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E196" t="n">
         <v>5</v>
@@ -9447,16 +9447,16 @@
         <v>12</v>
       </c>
       <c r="K196" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L196" t="n">
         <v>103</v>
       </c>
       <c r="M196" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="N196" t="n">
-        <v>82.5</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="197">
@@ -9515,7 +9515,7 @@
         <v>22</v>
       </c>
       <c r="C198" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D198" t="n">
         <v>7</v>
@@ -9533,22 +9533,22 @@
         <v>0</v>
       </c>
       <c r="I198" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J198" t="n">
         <v>5</v>
       </c>
       <c r="K198" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L198" t="n">
         <v>62</v>
       </c>
       <c r="M198" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="N198" t="n">
-        <v>79</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="199">
@@ -9564,7 +9564,7 @@
         <v>13</v>
       </c>
       <c r="D199" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E199" t="n">
         <v>4</v>
@@ -9582,19 +9582,19 @@
         <v>5</v>
       </c>
       <c r="J199" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K199" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L199" t="n">
         <v>58</v>
       </c>
       <c r="M199" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N199" t="n">
-        <v>79.3</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="200">
@@ -9607,13 +9607,13 @@
         <v>14</v>
       </c>
       <c r="C200" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D200" t="n">
         <v>4</v>
       </c>
       <c r="E200" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F200" t="n">
         <v>1</v>
@@ -9631,16 +9631,16 @@
         <v>4</v>
       </c>
       <c r="K200" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L200" t="n">
         <v>44</v>
       </c>
       <c r="M200" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N200" t="n">
-        <v>77.3</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="201">
@@ -9696,16 +9696,16 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C202" t="n">
         <v>68</v>
       </c>
       <c r="D202" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E202" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F202" t="n">
         <v>3</v>
@@ -9723,16 +9723,16 @@
         <v>14</v>
       </c>
       <c r="K202" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L202" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="M202" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="N202" t="n">
-        <v>74.2</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="203">
@@ -9788,13 +9788,13 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C204" t="n">
         <v>43</v>
       </c>
       <c r="D204" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E204" t="n">
         <v>7</v>
@@ -9815,16 +9815,16 @@
         <v>8</v>
       </c>
       <c r="K204" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L204" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M204" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="N204" t="n">
-        <v>82.7</v>
+        <v>80.59999999999999</v>
       </c>
     </row>
     <row r="205">
@@ -9880,7 +9880,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C206" t="n">
         <v>10</v>
@@ -9907,16 +9907,16 @@
         <v>2</v>
       </c>
       <c r="K206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L206" t="n">
         <v>25</v>
       </c>
       <c r="M206" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N206" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="207">
@@ -10039,13 +10039,13 @@
         <v>0</v>
       </c>
       <c r="I209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J209" t="n">
         <v>3</v>
       </c>
       <c r="K209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L209" t="n">
         <v>15</v>
@@ -10180,10 +10180,10 @@
         <v>4</v>
       </c>
       <c r="J212" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K212" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L212" t="n">
         <v>20</v>
@@ -10202,7 +10202,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C213" t="n">
         <v>6</v>
@@ -10229,16 +10229,16 @@
         <v>1</v>
       </c>
       <c r="K213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L213" t="n">
         <v>17</v>
       </c>
       <c r="M213" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N213" t="n">
-        <v>88.2</v>
+        <v>82.40000000000001</v>
       </c>
     </row>
     <row r="214">
@@ -10343,7 +10343,7 @@
         <v>5</v>
       </c>
       <c r="C216" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D216" t="n">
         <v>6</v>
@@ -10367,16 +10367,16 @@
         <v>3</v>
       </c>
       <c r="K216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L216" t="n">
         <v>27</v>
       </c>
       <c r="M216" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N216" t="n">
-        <v>81.5</v>
+        <v>77.8</v>
       </c>
     </row>
     <row r="217">
@@ -10438,7 +10438,7 @@
         <v>25</v>
       </c>
       <c r="D218" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E218" t="n">
         <v>1</v>
@@ -10456,19 +10456,19 @@
         <v>3</v>
       </c>
       <c r="J218" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L218" t="n">
         <v>53</v>
       </c>
       <c r="M218" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N218" t="n">
-        <v>79.2</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="219">
@@ -10484,7 +10484,7 @@
         <v>15</v>
       </c>
       <c r="D219" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E219" t="n">
         <v>0</v>
@@ -10505,16 +10505,16 @@
         <v>4</v>
       </c>
       <c r="K219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L219" t="n">
         <v>33</v>
       </c>
       <c r="M219" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N219" t="n">
-        <v>75.8</v>
+        <v>72.7</v>
       </c>
     </row>
     <row r="220">
@@ -10662,10 +10662,10 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C223" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D223" t="n">
         <v>3</v>
@@ -10689,16 +10689,16 @@
         <v>2</v>
       </c>
       <c r="K223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L223" t="n">
         <v>29</v>
       </c>
       <c r="M223" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N223" t="n">
-        <v>93.09999999999999</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="224">
@@ -10711,7 +10711,7 @@
         <v>7</v>
       </c>
       <c r="C224" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D224" t="n">
         <v>2</v>
@@ -10735,16 +10735,16 @@
         <v>1</v>
       </c>
       <c r="K224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L224" t="n">
         <v>25</v>
       </c>
       <c r="M224" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N224" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="225">
@@ -10824,10 +10824,10 @@
         <v>3</v>
       </c>
       <c r="J226" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L226" t="n">
         <v>23</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C228" t="n">
         <v>12</v>
@@ -10922,13 +10922,13 @@
         <v>1</v>
       </c>
       <c r="L228" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M228" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N228" t="n">
-        <v>76.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
     </row>
     <row r="229">
@@ -10990,7 +10990,7 @@
         <v>10</v>
       </c>
       <c r="D230" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E230" t="n">
         <v>1</v>
@@ -11011,16 +11011,16 @@
         <v>4</v>
       </c>
       <c r="K230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L230" t="n">
         <v>38</v>
       </c>
       <c r="M230" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N230" t="n">
-        <v>76.3</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="231">
@@ -11030,7 +11030,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C231" t="n">
         <v>17</v>
@@ -11039,10 +11039,10 @@
         <v>11</v>
       </c>
       <c r="E231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F231" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -11057,16 +11057,16 @@
         <v>7</v>
       </c>
       <c r="K231" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L231" t="n">
         <v>65</v>
       </c>
       <c r="M231" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="N231" t="n">
-        <v>78.5</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="232">
@@ -11122,10 +11122,10 @@
         </is>
       </c>
       <c r="B233" t="n">
+        <v>25</v>
+      </c>
+      <c r="C233" t="n">
         <v>26</v>
-      </c>
-      <c r="C233" t="n">
-        <v>29</v>
       </c>
       <c r="D233" t="n">
         <v>12</v>
@@ -11146,19 +11146,19 @@
         <v>6</v>
       </c>
       <c r="J233" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K233" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L233" t="n">
         <v>86</v>
       </c>
       <c r="M233" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N233" t="n">
-        <v>82.59999999999999</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="234">
@@ -11171,7 +11171,7 @@
         <v>15</v>
       </c>
       <c r="C234" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D234" t="n">
         <v>6</v>
@@ -11195,16 +11195,16 @@
         <v>5</v>
       </c>
       <c r="K234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L234" t="n">
         <v>50</v>
       </c>
       <c r="M234" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N234" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="235">
@@ -11266,37 +11266,37 @@
         <v>43</v>
       </c>
       <c r="D236" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E236" t="n">
+        <v>9</v>
+      </c>
+      <c r="F236" t="n">
+        <v>2</v>
+      </c>
+      <c r="G236" t="n">
+        <v>2</v>
+      </c>
+      <c r="H236" t="n">
+        <v>3</v>
+      </c>
+      <c r="I236" t="n">
+        <v>12</v>
+      </c>
+      <c r="J236" t="n">
+        <v>21</v>
+      </c>
+      <c r="K236" t="n">
         <v>10</v>
-      </c>
-      <c r="F236" t="n">
-        <v>2</v>
-      </c>
-      <c r="G236" t="n">
-        <v>2</v>
-      </c>
-      <c r="H236" t="n">
-        <v>3</v>
-      </c>
-      <c r="I236" t="n">
-        <v>13</v>
-      </c>
-      <c r="J236" t="n">
-        <v>23</v>
-      </c>
-      <c r="K236" t="n">
-        <v>5</v>
       </c>
       <c r="L236" t="n">
         <v>187</v>
       </c>
       <c r="M236" t="n">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N236" t="n">
-        <v>78.09999999999999</v>
+        <v>77</v>
       </c>
     </row>
     <row r="237">
@@ -11306,7 +11306,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C237" t="n">
         <v>19</v>
@@ -11324,7 +11324,7 @@
         <v>1</v>
       </c>
       <c r="H237" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I237" t="n">
         <v>8</v>
@@ -11333,16 +11333,16 @@
         <v>12</v>
       </c>
       <c r="K237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L237" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M237" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="N237" t="n">
-        <v>77</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="238">
@@ -11352,7 +11352,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C238" t="n">
         <v>33</v>
@@ -11373,22 +11373,22 @@
         <v>1</v>
       </c>
       <c r="I238" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J238" t="n">
         <v>12</v>
       </c>
       <c r="K238" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L238" t="n">
         <v>120</v>
       </c>
       <c r="M238" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N238" t="n">
-        <v>75</v>
+        <v>74.2</v>
       </c>
     </row>
     <row r="239">
@@ -11444,16 +11444,16 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C240" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D240" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E240" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F240" t="n">
         <v>2</v>
@@ -11468,19 +11468,19 @@
         <v>16</v>
       </c>
       <c r="J240" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="K240" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L240" t="n">
         <v>149</v>
       </c>
       <c r="M240" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N240" t="n">
-        <v>75.8</v>
+        <v>72.5</v>
       </c>
     </row>
     <row r="241">
@@ -11514,10 +11514,10 @@
         <v>7</v>
       </c>
       <c r="J241" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K241" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L241" t="n">
         <v>65</v>
@@ -11539,7 +11539,7 @@
         <v>15</v>
       </c>
       <c r="C242" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D242" t="n">
         <v>7</v>
@@ -11563,16 +11563,16 @@
         <v>3</v>
       </c>
       <c r="K242" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L242" t="n">
         <v>71</v>
       </c>
       <c r="M242" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="N242" t="n">
-        <v>85.90000000000001</v>
+        <v>81.7</v>
       </c>
     </row>
     <row r="243">
@@ -11628,7 +11628,7 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C244" t="n">
         <v>12</v>
@@ -11655,16 +11655,16 @@
         <v>3</v>
       </c>
       <c r="K244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L244" t="n">
         <v>39</v>
       </c>
       <c r="M244" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N244" t="n">
-        <v>82.09999999999999</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="245">
@@ -11720,13 +11720,13 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C246" t="n">
         <v>54</v>
       </c>
       <c r="D246" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E246" t="n">
         <v>5</v>
@@ -11747,16 +11747,16 @@
         <v>29</v>
       </c>
       <c r="K246" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L246" t="n">
         <v>175</v>
       </c>
       <c r="M246" t="n">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="N246" t="n">
-        <v>70.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
     </row>
     <row r="247">
@@ -11772,7 +11772,7 @@
         <v>16</v>
       </c>
       <c r="D247" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E247" t="n">
         <v>0</v>
@@ -11793,16 +11793,16 @@
         <v>3</v>
       </c>
       <c r="K247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L247" t="n">
         <v>43</v>
       </c>
       <c r="M247" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N247" t="n">
-        <v>81.40000000000001</v>
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="248">
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C249" t="n">
         <v>20</v>
@@ -11879,22 +11879,22 @@
         <v>0</v>
       </c>
       <c r="I249" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J249" t="n">
         <v>8</v>
       </c>
       <c r="K249" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L249" t="n">
         <v>59</v>
       </c>
       <c r="M249" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N249" t="n">
-        <v>72.90000000000001</v>
+        <v>71.2</v>
       </c>
     </row>
     <row r="250">
@@ -11904,13 +11904,13 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C250" t="n">
         <v>11</v>
       </c>
       <c r="D250" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E250" t="n">
         <v>2</v>
@@ -11931,16 +11931,16 @@
         <v>6</v>
       </c>
       <c r="K250" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L250" t="n">
         <v>38</v>
       </c>
       <c r="M250" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="N250" t="n">
-        <v>76.3</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="251">
@@ -12091,7 +12091,7 @@
         <v>12</v>
       </c>
       <c r="C254" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D254" t="n">
         <v>2</v>
@@ -12109,22 +12109,22 @@
         <v>0</v>
       </c>
       <c r="I254" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J254" t="n">
         <v>2</v>
       </c>
       <c r="K254" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L254" t="n">
         <v>50</v>
       </c>
       <c r="M254" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N254" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="255">
@@ -12134,16 +12134,16 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C255" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D255" t="n">
         <v>9</v>
       </c>
       <c r="E255" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F255" t="n">
         <v>6</v>
@@ -12161,16 +12161,16 @@
         <v>23</v>
       </c>
       <c r="K255" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L255" t="n">
         <v>144</v>
       </c>
       <c r="M255" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="N255" t="n">
-        <v>71.5</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="256">
@@ -12183,13 +12183,13 @@
         <v>73</v>
       </c>
       <c r="C256" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D256" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E256" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F256" t="n">
         <v>9</v>
@@ -12201,22 +12201,22 @@
         <v>2</v>
       </c>
       <c r="I256" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J256" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K256" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L256" t="n">
         <v>222</v>
       </c>
       <c r="M256" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N256" t="n">
-        <v>74.8</v>
+        <v>74.3</v>
       </c>
     </row>
     <row r="257">
@@ -12367,10 +12367,10 @@
         <v>103</v>
       </c>
       <c r="C260" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D260" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E260" t="n">
         <v>8</v>
@@ -12382,25 +12382,25 @@
         <v>5</v>
       </c>
       <c r="H260" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I260" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J260" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K260" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L260" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="M260" t="n">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="N260" t="n">
-        <v>76.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="261">
@@ -12410,43 +12410,43 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>508</v>
+        <v>487</v>
       </c>
       <c r="C261" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D261" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E261" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F261" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G261" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H261" t="n">
         <v>16</v>
       </c>
       <c r="I261" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="J261" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="K261" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="L261" t="n">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="M261" t="n">
-        <v>889</v>
+        <v>855</v>
       </c>
       <c r="N261" t="n">
-        <v>76.40000000000001</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="262">
@@ -12456,43 +12456,43 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C262" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D262" t="n">
+        <v>16</v>
+      </c>
+      <c r="E262" t="n">
+        <v>3</v>
+      </c>
+      <c r="F262" t="n">
+        <v>6</v>
+      </c>
+      <c r="G262" t="n">
+        <v>0</v>
+      </c>
+      <c r="H262" t="n">
+        <v>3</v>
+      </c>
+      <c r="I262" t="n">
+        <v>13</v>
+      </c>
+      <c r="J262" t="n">
         <v>17</v>
       </c>
-      <c r="E262" t="n">
-        <v>3</v>
-      </c>
-      <c r="F262" t="n">
-        <v>7</v>
-      </c>
-      <c r="G262" t="n">
-        <v>0</v>
-      </c>
-      <c r="H262" t="n">
-        <v>3</v>
-      </c>
-      <c r="I262" t="n">
-        <v>15</v>
-      </c>
-      <c r="J262" t="n">
-        <v>19</v>
-      </c>
       <c r="K262" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="L262" t="n">
         <v>157</v>
       </c>
       <c r="M262" t="n">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="N262" t="n">
-        <v>76.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="263">
@@ -12502,13 +12502,13 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C263" t="n">
         <v>39</v>
       </c>
       <c r="D263" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E263" t="n">
         <v>3</v>
@@ -12529,16 +12529,16 @@
         <v>17</v>
       </c>
       <c r="K263" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L263" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M263" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="N263" t="n">
-        <v>76.2</v>
+        <v>75.40000000000001</v>
       </c>
     </row>
     <row r="264">
@@ -12548,13 +12548,13 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C264" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D264" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E264" t="n">
         <v>6</v>
@@ -12575,16 +12575,16 @@
         <v>23</v>
       </c>
       <c r="K264" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L264" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M264" t="n">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="N264" t="n">
-        <v>79.3</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="265">
@@ -12594,10 +12594,10 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C265" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D265" t="n">
         <v>26</v>
@@ -12618,19 +12618,19 @@
         <v>19</v>
       </c>
       <c r="J265" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K265" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L265" t="n">
         <v>268</v>
       </c>
       <c r="M265" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N265" t="n">
-        <v>79.09999999999999</v>
+        <v>78</v>
       </c>
     </row>
     <row r="266">
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C267" t="n">
         <v>42</v>
@@ -12707,22 +12707,22 @@
         <v>0</v>
       </c>
       <c r="I267" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J267" t="n">
         <v>12</v>
       </c>
       <c r="K267" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L267" t="n">
         <v>131</v>
       </c>
       <c r="M267" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N267" t="n">
-        <v>79.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="268">
@@ -12756,10 +12756,10 @@
         <v>6</v>
       </c>
       <c r="J268" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L268" t="n">
         <v>66</v>
@@ -12830,7 +12830,7 @@
         <v>19</v>
       </c>
       <c r="D270" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E270" t="n">
         <v>4</v>
@@ -12851,16 +12851,16 @@
         <v>6</v>
       </c>
       <c r="K270" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L270" t="n">
         <v>64</v>
       </c>
       <c r="M270" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N270" t="n">
-        <v>82.8</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="271">
@@ -12894,10 +12894,10 @@
         <v>3</v>
       </c>
       <c r="J271" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K271" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L271" t="n">
         <v>49</v>
@@ -12965,7 +12965,7 @@
         <v>2</v>
       </c>
       <c r="C273" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D273" t="n">
         <v>2</v>
@@ -12989,16 +12989,16 @@
         <v>6</v>
       </c>
       <c r="K273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L273" t="n">
         <v>29</v>
       </c>
       <c r="M273" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N273" t="n">
-        <v>65.5</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="274">
@@ -13014,13 +13014,13 @@
         <v>41</v>
       </c>
       <c r="D274" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E274" t="n">
         <v>4</v>
       </c>
       <c r="F274" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G274" t="n">
         <v>0</v>
@@ -13035,16 +13035,16 @@
         <v>28</v>
       </c>
       <c r="K274" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L274" t="n">
         <v>228</v>
       </c>
       <c r="M274" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="N274" t="n">
-        <v>75.90000000000001</v>
+        <v>75</v>
       </c>
     </row>
     <row r="275">
@@ -13054,7 +13054,7 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C275" t="n">
         <v>40</v>
@@ -13078,19 +13078,19 @@
         <v>25</v>
       </c>
       <c r="J275" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K275" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="L275" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="M275" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="N275" t="n">
-        <v>79.59999999999999</v>
+        <v>78.40000000000001</v>
       </c>
     </row>
     <row r="276">
@@ -13100,7 +13100,7 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C276" t="n">
         <v>30</v>
@@ -13124,19 +13124,19 @@
         <v>8</v>
       </c>
       <c r="J276" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K276" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L276" t="n">
         <v>85</v>
       </c>
       <c r="M276" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N276" t="n">
-        <v>70.59999999999999</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="277">
@@ -13155,7 +13155,7 @@
         <v>13</v>
       </c>
       <c r="E277" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F277" t="n">
         <v>1</v>
@@ -13173,16 +13173,16 @@
         <v>17</v>
       </c>
       <c r="K277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L277" t="n">
         <v>100</v>
       </c>
       <c r="M277" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N277" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="278">
@@ -13192,10 +13192,10 @@
         </is>
       </c>
       <c r="B278" t="n">
+        <v>33</v>
+      </c>
+      <c r="C278" t="n">
         <v>34</v>
-      </c>
-      <c r="C278" t="n">
-        <v>35</v>
       </c>
       <c r="D278" t="n">
         <v>2</v>
@@ -13219,16 +13219,16 @@
         <v>8</v>
       </c>
       <c r="K278" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L278" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M278" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="N278" t="n">
-        <v>78.5</v>
+        <v>77.2</v>
       </c>
     </row>
     <row r="279">
@@ -13284,7 +13284,7 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C280" t="n">
         <v>9</v>
@@ -13305,22 +13305,22 @@
         <v>0</v>
       </c>
       <c r="I280" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J280" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K280" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L280" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M280" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="N280" t="n">
-        <v>80.09999999999999</v>
+        <v>78.59999999999999</v>
       </c>
     </row>
     <row r="281">
@@ -13330,7 +13330,7 @@
         </is>
       </c>
       <c r="B281" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C281" t="n">
         <v>47</v>
@@ -13342,7 +13342,7 @@
         <v>3</v>
       </c>
       <c r="F281" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G281" t="n">
         <v>0</v>
@@ -13351,22 +13351,22 @@
         <v>1</v>
       </c>
       <c r="I281" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J281" t="n">
         <v>20</v>
       </c>
       <c r="K281" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L281" t="n">
         <v>155</v>
       </c>
       <c r="M281" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N281" t="n">
-        <v>76.8</v>
+        <v>75.5</v>
       </c>
     </row>
     <row r="282">
@@ -13379,10 +13379,10 @@
         <v>21</v>
       </c>
       <c r="C282" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D282" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E282" t="n">
         <v>3</v>
@@ -13403,16 +13403,16 @@
         <v>17</v>
       </c>
       <c r="K282" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L282" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M282" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N282" t="n">
-        <v>72.2</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="283">
@@ -13446,10 +13446,10 @@
         <v>13</v>
       </c>
       <c r="J283" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K283" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L283" t="n">
         <v>102</v>
@@ -13489,13 +13489,13 @@
         <v>0</v>
       </c>
       <c r="I284" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J284" t="n">
         <v>12</v>
       </c>
       <c r="K284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L284" t="n">
         <v>94</v>
@@ -13560,16 +13560,16 @@
         </is>
       </c>
       <c r="B286" t="n">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C286" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D286" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E286" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F286" t="n">
         <v>6</v>
@@ -13587,16 +13587,16 @@
         <v>24</v>
       </c>
       <c r="K286" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="L286" t="n">
         <v>291</v>
       </c>
       <c r="M286" t="n">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="N286" t="n">
-        <v>83.2</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="287">
@@ -13606,7 +13606,7 @@
         </is>
       </c>
       <c r="B287" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C287" t="n">
         <v>10</v>
@@ -13633,16 +13633,16 @@
         <v>4</v>
       </c>
       <c r="K287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L287" t="n">
         <v>25</v>
       </c>
       <c r="M287" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N287" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="288">
@@ -13652,7 +13652,7 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C288" t="n">
         <v>16</v>
@@ -13679,16 +13679,16 @@
         <v>2</v>
       </c>
       <c r="K288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L288" t="n">
         <v>34</v>
       </c>
       <c r="M288" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="N288" t="n">
-        <v>88.2</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="289">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C289" t="n">
         <v>30</v>
       </c>
       <c r="D289" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E289" t="n">
         <v>4</v>
@@ -13725,16 +13725,16 @@
         <v>11</v>
       </c>
       <c r="K289" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L289" t="n">
         <v>100</v>
       </c>
       <c r="M289" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="N289" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="290">
@@ -13747,13 +13747,13 @@
         <v>195</v>
       </c>
       <c r="C290" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D290" t="n">
         <v>8</v>
       </c>
       <c r="E290" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F290" t="n">
         <v>13</v>
@@ -13771,16 +13771,16 @@
         <v>17</v>
       </c>
       <c r="K290" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L290" t="n">
         <v>302</v>
       </c>
       <c r="M290" t="n">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="N290" t="n">
-        <v>89.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="291">
@@ -13790,7 +13790,7 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C291" t="n">
         <v>23</v>
@@ -13808,7 +13808,7 @@
         <v>0</v>
       </c>
       <c r="H291" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I291" t="n">
         <v>10</v>
@@ -13817,16 +13817,16 @@
         <v>13</v>
       </c>
       <c r="K291" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L291" t="n">
         <v>122</v>
       </c>
       <c r="M291" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="N291" t="n">
-        <v>79.5</v>
+        <v>77.90000000000001</v>
       </c>
     </row>
     <row r="292">
@@ -13974,13 +13974,13 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C295" t="n">
         <v>40</v>
       </c>
       <c r="D295" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E295" t="n">
         <v>4</v>
@@ -13995,22 +13995,22 @@
         <v>1</v>
       </c>
       <c r="I295" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J295" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K295" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L295" t="n">
         <v>134</v>
       </c>
       <c r="M295" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="N295" t="n">
-        <v>73.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="296">
@@ -14020,13 +14020,13 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C296" t="n">
         <v>30</v>
       </c>
       <c r="D296" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E296" t="n">
         <v>3</v>
@@ -14047,16 +14047,16 @@
         <v>14</v>
       </c>
       <c r="K296" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L296" t="n">
         <v>122</v>
       </c>
       <c r="M296" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="N296" t="n">
-        <v>73</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="297">
@@ -14437,7 +14437,7 @@
         <v>7</v>
       </c>
       <c r="C305" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D305" t="n">
         <v>5</v>
@@ -14461,16 +14461,16 @@
         <v>9</v>
       </c>
       <c r="K305" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L305" t="n">
         <v>72</v>
       </c>
       <c r="M305" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N305" t="n">
-        <v>70.8</v>
+        <v>69.40000000000001</v>
       </c>
     </row>
     <row r="306">
@@ -14483,7 +14483,7 @@
         <v>20</v>
       </c>
       <c r="C306" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D306" t="n">
         <v>9</v>
@@ -14507,16 +14507,16 @@
         <v>7</v>
       </c>
       <c r="K306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L306" t="n">
         <v>78</v>
       </c>
       <c r="M306" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="N306" t="n">
-        <v>83.3</v>
+        <v>82.09999999999999</v>
       </c>
     </row>
     <row r="307">
@@ -14685,13 +14685,13 @@
         <v>2</v>
       </c>
       <c r="I310" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J310" t="n">
         <v>16</v>
       </c>
       <c r="K310" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L310" t="n">
         <v>109</v>
@@ -14756,10 +14756,10 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C312" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D312" t="n">
         <v>9</v>
@@ -14777,22 +14777,22 @@
         <v>1</v>
       </c>
       <c r="I312" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J312" t="n">
         <v>23</v>
       </c>
       <c r="K312" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L312" t="n">
         <v>149</v>
       </c>
       <c r="M312" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="N312" t="n">
-        <v>66.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="313">
@@ -14802,7 +14802,7 @@
         </is>
       </c>
       <c r="B313" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C313" t="n">
         <v>70</v>
@@ -14811,7 +14811,7 @@
         <v>33</v>
       </c>
       <c r="E313" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F313" t="n">
         <v>7</v>
@@ -14823,22 +14823,22 @@
         <v>1</v>
       </c>
       <c r="I313" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J313" t="n">
         <v>22</v>
       </c>
       <c r="K313" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L313" t="n">
         <v>232</v>
       </c>
       <c r="M313" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="N313" t="n">
-        <v>78.90000000000001</v>
+        <v>78</v>
       </c>
     </row>
     <row r="314">
@@ -14848,10 +14848,10 @@
         </is>
       </c>
       <c r="B314" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C314" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D314" t="n">
         <v>35</v>
@@ -14866,25 +14866,25 @@
         <v>2</v>
       </c>
       <c r="H314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I314" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J314" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K314" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L314" t="n">
         <v>210</v>
       </c>
       <c r="M314" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="N314" t="n">
-        <v>71.90000000000001</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="315">
@@ -14894,10 +14894,10 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C315" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D315" t="n">
         <v>13</v>
@@ -14921,16 +14921,16 @@
         <v>24</v>
       </c>
       <c r="K315" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L315" t="n">
         <v>127</v>
       </c>
       <c r="M315" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="N315" t="n">
-        <v>61.4</v>
+        <v>59.8</v>
       </c>
     </row>
     <row r="316">
@@ -14940,10 +14940,10 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C316" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D316" t="n">
         <v>10</v>
@@ -14967,16 +14967,16 @@
         <v>2</v>
       </c>
       <c r="K316" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L316" t="n">
         <v>59</v>
       </c>
       <c r="M316" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N316" t="n">
-        <v>72.90000000000001</v>
+        <v>69.5</v>
       </c>
     </row>
     <row r="317">
@@ -15032,13 +15032,13 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C318" t="n">
         <v>18</v>
       </c>
       <c r="D318" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E318" t="n">
         <v>2</v>
@@ -15059,16 +15059,16 @@
         <v>6</v>
       </c>
       <c r="K318" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="L318" t="n">
         <v>91</v>
       </c>
       <c r="M318" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="N318" t="n">
-        <v>50.5</v>
+        <v>48.4</v>
       </c>
     </row>
     <row r="319">
@@ -15197,16 +15197,16 @@
         <v>1</v>
       </c>
       <c r="K321" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L321" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M321" t="n">
         <v>17</v>
       </c>
       <c r="N321" t="n">
-        <v>53.1</v>
+        <v>54.8</v>
       </c>
     </row>
     <row r="322">
@@ -15219,7 +15219,7 @@
         <v>2</v>
       </c>
       <c r="C322" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D322" t="n">
         <v>2</v>
@@ -15243,16 +15243,16 @@
         <v>0</v>
       </c>
       <c r="K322" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L322" t="n">
         <v>16</v>
       </c>
       <c r="M322" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N322" t="n">
-        <v>62.5</v>
+        <v>56.2</v>
       </c>
     </row>
     <row r="323">
@@ -15372,25 +15372,25 @@
         <v>0</v>
       </c>
       <c r="H325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I325" t="n">
         <v>2</v>
       </c>
       <c r="J325" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K325" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L325" t="n">
         <v>20</v>
       </c>
       <c r="M325" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N325" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="326">
@@ -15452,7 +15452,7 @@
         <v>3</v>
       </c>
       <c r="D327" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E327" t="n">
         <v>1</v>
@@ -15476,13 +15476,13 @@
         <v>14</v>
       </c>
       <c r="L327" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M327" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N327" t="n">
-        <v>27.3</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="328">
@@ -15590,7 +15590,7 @@
         <v>6</v>
       </c>
       <c r="D330" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E330" t="n">
         <v>2</v>
@@ -15608,19 +15608,19 @@
         <v>3</v>
       </c>
       <c r="J330" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K330" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L330" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M330" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N330" t="n">
-        <v>39</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="331">
@@ -17277,6 +17277,52 @@
       </c>
       <c r="N366" t="n">
         <v>42.7</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>0</v>
+      </c>
+      <c r="C367" t="n">
+        <v>0</v>
+      </c>
+      <c r="D367" t="n">
+        <v>1</v>
+      </c>
+      <c r="E367" t="n">
+        <v>0</v>
+      </c>
+      <c r="F367" t="n">
+        <v>0</v>
+      </c>
+      <c r="G367" t="n">
+        <v>0</v>
+      </c>
+      <c r="H367" t="n">
+        <v>0</v>
+      </c>
+      <c r="I367" t="n">
+        <v>0</v>
+      </c>
+      <c r="J367" t="n">
+        <v>0</v>
+      </c>
+      <c r="K367" t="n">
+        <v>0</v>
+      </c>
+      <c r="L367" t="n">
+        <v>1</v>
+      </c>
+      <c r="M367" t="n">
+        <v>1</v>
+      </c>
+      <c r="N367" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -17290,7 +17336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M909"/>
+  <dimension ref="A1:M910"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25880,7 +25926,7 @@
         <v>16</v>
       </c>
       <c r="D191" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E191" t="n">
         <v>13</v>
@@ -25895,16 +25941,16 @@
         <v>0</v>
       </c>
       <c r="I191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J191" t="n">
         <v>10</v>
       </c>
       <c r="K191" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L191" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M191" t="n">
         <v>79</v>
@@ -26012,13 +26058,13 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D194" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E194" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F194" t="n">
         <v>5</v>
@@ -26039,7 +26085,7 @@
         <v>12</v>
       </c>
       <c r="L194" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M194" t="n">
         <v>102</v>
@@ -26105,7 +26151,7 @@
         <v>22</v>
       </c>
       <c r="D196" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E196" t="n">
         <v>7</v>
@@ -26123,13 +26169,13 @@
         <v>0</v>
       </c>
       <c r="J196" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K196" t="n">
         <v>5</v>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M196" t="n">
         <v>62</v>
@@ -26153,7 +26199,7 @@
         <v>13</v>
       </c>
       <c r="E197" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F197" t="n">
         <v>4</v>
@@ -26171,10 +26217,10 @@
         <v>5</v>
       </c>
       <c r="K197" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L197" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M197" t="n">
         <v>57</v>
@@ -26195,13 +26241,13 @@
         <v>14</v>
       </c>
       <c r="D198" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E198" t="n">
         <v>4</v>
       </c>
       <c r="F198" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G198" t="n">
         <v>1</v>
@@ -26219,7 +26265,7 @@
         <v>4</v>
       </c>
       <c r="L198" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M198" t="n">
         <v>44</v>
@@ -26282,16 +26328,16 @@
         </is>
       </c>
       <c r="C200" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D200" t="n">
         <v>68</v>
       </c>
       <c r="E200" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F200" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G200" t="n">
         <v>3</v>
@@ -26309,10 +26355,10 @@
         <v>14</v>
       </c>
       <c r="L200" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M200" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="201">
@@ -26372,13 +26418,13 @@
         </is>
       </c>
       <c r="C202" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D202" t="n">
         <v>43</v>
       </c>
       <c r="E202" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F202" t="n">
         <v>7</v>
@@ -26399,10 +26445,10 @@
         <v>8</v>
       </c>
       <c r="L202" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M202" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="203">
@@ -26462,7 +26508,7 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D204" t="n">
         <v>10</v>
@@ -26489,7 +26535,7 @@
         <v>2</v>
       </c>
       <c r="L204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M204" t="n">
         <v>25</v>
@@ -26618,13 +26664,13 @@
         <v>0</v>
       </c>
       <c r="J207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K207" t="n">
         <v>3</v>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M207" t="n">
         <v>15</v>
@@ -26756,10 +26802,10 @@
         <v>4</v>
       </c>
       <c r="K210" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M210" t="n">
         <v>17</v>
@@ -26777,7 +26823,7 @@
         </is>
       </c>
       <c r="C211" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D211" t="n">
         <v>6</v>
@@ -26804,7 +26850,7 @@
         <v>1</v>
       </c>
       <c r="L211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M211" t="n">
         <v>17</v>
@@ -26915,7 +26961,7 @@
         <v>5</v>
       </c>
       <c r="D214" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E214" t="n">
         <v>6</v>
@@ -26939,7 +26985,7 @@
         <v>3</v>
       </c>
       <c r="L214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M214" t="n">
         <v>27</v>
@@ -26963,7 +27009,7 @@
         <v>25</v>
       </c>
       <c r="E215" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F215" t="n">
         <v>1</v>
@@ -26981,10 +27027,10 @@
         <v>3</v>
       </c>
       <c r="K215" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M215" t="n">
         <v>53</v>
@@ -27008,7 +27054,7 @@
         <v>15</v>
       </c>
       <c r="E216" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F216" t="n">
         <v>0</v>
@@ -27029,7 +27075,7 @@
         <v>4</v>
       </c>
       <c r="L216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M216" t="n">
         <v>33</v>
@@ -27182,10 +27228,10 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D220" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E220" t="n">
         <v>3</v>
@@ -27209,7 +27255,7 @@
         <v>2</v>
       </c>
       <c r="L220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M220" t="n">
         <v>29</v>
@@ -27230,7 +27276,7 @@
         <v>7</v>
       </c>
       <c r="D221" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E221" t="n">
         <v>2</v>
@@ -27254,7 +27300,7 @@
         <v>1</v>
       </c>
       <c r="L221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M221" t="n">
         <v>25</v>
@@ -27341,10 +27387,10 @@
         <v>3</v>
       </c>
       <c r="K223" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L223" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M223" t="n">
         <v>23</v>
@@ -27407,7 +27453,7 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D225" t="n">
         <v>10</v>
@@ -27437,7 +27483,7 @@
         <v>1</v>
       </c>
       <c r="M225" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="226">
@@ -27503,7 +27549,7 @@
         <v>10</v>
       </c>
       <c r="E227" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F227" t="n">
         <v>1</v>
@@ -27524,7 +27570,7 @@
         <v>3</v>
       </c>
       <c r="L227" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M227" t="n">
         <v>33</v>
@@ -27542,7 +27588,7 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D228" t="n">
         <v>17</v>
@@ -27551,10 +27597,10 @@
         <v>11</v>
       </c>
       <c r="F228" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G228" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -27569,7 +27615,7 @@
         <v>7</v>
       </c>
       <c r="L228" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M228" t="n">
         <v>63</v>
@@ -27590,7 +27636,7 @@
         <v>15</v>
       </c>
       <c r="D229" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E229" t="n">
         <v>7</v>
@@ -27611,10 +27657,10 @@
         <v>6</v>
       </c>
       <c r="K229" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L229" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M229" t="n">
         <v>67</v>
@@ -27635,7 +27681,7 @@
         <v>15</v>
       </c>
       <c r="D230" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E230" t="n">
         <v>4</v>
@@ -27659,7 +27705,7 @@
         <v>4</v>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M230" t="n">
         <v>43</v>
@@ -27728,7 +27774,7 @@
         <v>10</v>
       </c>
       <c r="E232" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F232" t="n">
         <v>0</v>
@@ -27749,7 +27795,7 @@
         <v>0</v>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M232" t="n">
         <v>23</v>
@@ -27767,7 +27813,7 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D233" t="n">
         <v>6</v>
@@ -27794,7 +27840,7 @@
         <v>3</v>
       </c>
       <c r="L233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M233" t="n">
         <v>29</v>
@@ -27833,13 +27879,13 @@
         <v>0</v>
       </c>
       <c r="J234" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K234" t="n">
         <v>4</v>
       </c>
       <c r="L234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M234" t="n">
         <v>59</v>
@@ -27902,16 +27948,16 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D236" t="n">
         <v>39</v>
       </c>
       <c r="E236" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F236" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G236" t="n">
         <v>1</v>
@@ -27929,7 +27975,7 @@
         <v>7</v>
       </c>
       <c r="L236" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M236" t="n">
         <v>87</v>
@@ -27971,10 +28017,10 @@
         <v>3</v>
       </c>
       <c r="K237" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L237" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M237" t="n">
         <v>33</v>
@@ -27995,7 +28041,7 @@
         <v>8</v>
       </c>
       <c r="D238" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E238" t="n">
         <v>2</v>
@@ -28019,7 +28065,7 @@
         <v>0</v>
       </c>
       <c r="L238" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M238" t="n">
         <v>40</v>
@@ -28082,7 +28128,7 @@
         </is>
       </c>
       <c r="C240" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D240" t="n">
         <v>6</v>
@@ -28109,7 +28155,7 @@
         <v>2</v>
       </c>
       <c r="L240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M240" t="n">
         <v>17</v>
@@ -28178,7 +28224,7 @@
         <v>30</v>
       </c>
       <c r="E242" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F242" t="n">
         <v>3</v>
@@ -28199,7 +28245,7 @@
         <v>12</v>
       </c>
       <c r="L242" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M242" t="n">
         <v>78</v>
@@ -28307,7 +28353,7 @@
         </is>
       </c>
       <c r="C245" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D245" t="n">
         <v>16</v>
@@ -28328,13 +28374,13 @@
         <v>0</v>
       </c>
       <c r="J245" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K245" t="n">
         <v>7</v>
       </c>
       <c r="L245" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M245" t="n">
         <v>48</v>
@@ -28358,7 +28404,7 @@
         <v>8</v>
       </c>
       <c r="E246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F246" t="n">
         <v>2</v>
@@ -28379,7 +28425,7 @@
         <v>5</v>
       </c>
       <c r="L246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M246" t="n">
         <v>28</v>
@@ -28535,7 +28581,7 @@
         <v>10</v>
       </c>
       <c r="D250" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E250" t="n">
         <v>1</v>
@@ -28553,13 +28599,13 @@
         <v>0</v>
       </c>
       <c r="J250" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K250" t="n">
         <v>2</v>
       </c>
       <c r="L250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M250" t="n">
         <v>37</v>
@@ -28577,16 +28623,16 @@
         </is>
       </c>
       <c r="C251" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D251" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E251" t="n">
         <v>8</v>
       </c>
       <c r="F251" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G251" t="n">
         <v>6</v>
@@ -28604,7 +28650,7 @@
         <v>23</v>
       </c>
       <c r="L251" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M251" t="n">
         <v>138</v>
@@ -28625,13 +28671,13 @@
         <v>69</v>
       </c>
       <c r="D252" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E252" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F252" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G252" t="n">
         <v>9</v>
@@ -28643,13 +28689,13 @@
         <v>2</v>
       </c>
       <c r="J252" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K252" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L252" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M252" t="n">
         <v>212</v>
@@ -28805,10 +28851,10 @@
         <v>102</v>
       </c>
       <c r="D256" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E256" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F256" t="n">
         <v>8</v>
@@ -28820,19 +28866,19 @@
         <v>5</v>
       </c>
       <c r="I256" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J256" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K256" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L256" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="M256" t="n">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="257">
@@ -28847,37 +28893,37 @@
         </is>
       </c>
       <c r="C257" t="n">
-        <v>508</v>
+        <v>487</v>
       </c>
       <c r="D257" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E257" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="F257" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G257" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H257" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I257" t="n">
         <v>16</v>
       </c>
       <c r="J257" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K257" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="L257" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="M257" t="n">
-        <v>1164</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="258">
@@ -28892,34 +28938,34 @@
         </is>
       </c>
       <c r="C258" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D258" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E258" t="n">
+        <v>16</v>
+      </c>
+      <c r="F258" t="n">
+        <v>3</v>
+      </c>
+      <c r="G258" t="n">
+        <v>6</v>
+      </c>
+      <c r="H258" t="n">
+        <v>0</v>
+      </c>
+      <c r="I258" t="n">
+        <v>3</v>
+      </c>
+      <c r="J258" t="n">
+        <v>13</v>
+      </c>
+      <c r="K258" t="n">
         <v>17</v>
       </c>
-      <c r="F258" t="n">
-        <v>3</v>
-      </c>
-      <c r="G258" t="n">
-        <v>7</v>
-      </c>
-      <c r="H258" t="n">
-        <v>0</v>
-      </c>
-      <c r="I258" t="n">
-        <v>3</v>
-      </c>
-      <c r="J258" t="n">
-        <v>15</v>
-      </c>
-      <c r="K258" t="n">
-        <v>19</v>
-      </c>
       <c r="L258" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="M258" t="n">
         <v>157</v>
@@ -28937,13 +28983,13 @@
         </is>
       </c>
       <c r="C259" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D259" t="n">
         <v>39</v>
       </c>
       <c r="E259" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F259" t="n">
         <v>3</v>
@@ -28964,10 +29010,10 @@
         <v>17</v>
       </c>
       <c r="L259" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M259" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="260">
@@ -28982,13 +29028,13 @@
         </is>
       </c>
       <c r="C260" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D260" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E260" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F260" t="n">
         <v>6</v>
@@ -29009,10 +29055,10 @@
         <v>23</v>
       </c>
       <c r="L260" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M260" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="261">
@@ -29027,10 +29073,10 @@
         </is>
       </c>
       <c r="C261" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D261" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E261" t="n">
         <v>26</v>
@@ -29051,10 +29097,10 @@
         <v>19</v>
       </c>
       <c r="K261" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L261" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M261" t="n">
         <v>268</v>
@@ -29117,7 +29163,7 @@
         </is>
       </c>
       <c r="C263" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D263" t="n">
         <v>39</v>
@@ -29138,13 +29184,13 @@
         <v>0</v>
       </c>
       <c r="J263" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K263" t="n">
         <v>12</v>
       </c>
       <c r="L263" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M263" t="n">
         <v>123</v>
@@ -29186,10 +29232,10 @@
         <v>6</v>
       </c>
       <c r="K264" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M264" t="n">
         <v>66</v>
@@ -29258,7 +29304,7 @@
         <v>19</v>
       </c>
       <c r="E266" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F266" t="n">
         <v>3</v>
@@ -29279,7 +29325,7 @@
         <v>5</v>
       </c>
       <c r="L266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M266" t="n">
         <v>59</v>
@@ -29321,10 +29367,10 @@
         <v>3</v>
       </c>
       <c r="K267" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L267" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M267" t="n">
         <v>45</v>
@@ -29393,13 +29439,13 @@
         <v>18</v>
       </c>
       <c r="E269" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F269" t="n">
         <v>2</v>
       </c>
       <c r="G269" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -29414,7 +29460,7 @@
         <v>23</v>
       </c>
       <c r="L269" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M269" t="n">
         <v>181</v>
@@ -29432,7 +29478,7 @@
         </is>
       </c>
       <c r="C270" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D270" t="n">
         <v>32</v>
@@ -29456,13 +29502,13 @@
         <v>24</v>
       </c>
       <c r="K270" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L270" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M270" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="271">
@@ -29477,7 +29523,7 @@
         </is>
       </c>
       <c r="C271" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D271" t="n">
         <v>18</v>
@@ -29501,10 +29547,10 @@
         <v>7</v>
       </c>
       <c r="K271" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L271" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M271" t="n">
         <v>61</v>
@@ -29531,7 +29577,7 @@
         <v>10</v>
       </c>
       <c r="F272" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G272" t="n">
         <v>1</v>
@@ -29549,7 +29595,7 @@
         <v>9</v>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M272" t="n">
         <v>70</v>
@@ -29567,7 +29613,7 @@
         </is>
       </c>
       <c r="C273" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D273" t="n">
         <v>15</v>
@@ -29597,7 +29643,7 @@
         <v>3</v>
       </c>
       <c r="M273" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="274">
@@ -29612,7 +29658,7 @@
         </is>
       </c>
       <c r="C274" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D274" t="n">
         <v>6</v>
@@ -29633,16 +29679,16 @@
         <v>0</v>
       </c>
       <c r="J274" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K274" t="n">
         <v>10</v>
       </c>
       <c r="L274" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M274" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="275">
@@ -29657,7 +29703,7 @@
         </is>
       </c>
       <c r="C275" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D275" t="n">
         <v>32</v>
@@ -29669,7 +29715,7 @@
         <v>2</v>
       </c>
       <c r="G275" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -29678,13 +29724,13 @@
         <v>1</v>
       </c>
       <c r="J275" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K275" t="n">
         <v>11</v>
       </c>
       <c r="L275" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M275" t="n">
         <v>124</v>
@@ -29705,10 +29751,10 @@
         <v>18</v>
       </c>
       <c r="D276" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E276" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F276" t="n">
         <v>2</v>
@@ -29729,10 +29775,10 @@
         <v>4</v>
       </c>
       <c r="L276" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M276" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="277">
@@ -29771,10 +29817,10 @@
         <v>10</v>
       </c>
       <c r="K277" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L277" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M277" t="n">
         <v>88</v>
@@ -29813,13 +29859,13 @@
         <v>0</v>
       </c>
       <c r="J278" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K278" t="n">
         <v>7</v>
       </c>
       <c r="L278" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M278" t="n">
         <v>66</v>
@@ -29882,16 +29928,16 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D280" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E280" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F280" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G280" t="n">
         <v>5</v>
@@ -29909,7 +29955,7 @@
         <v>20</v>
       </c>
       <c r="L280" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M280" t="n">
         <v>267</v>
@@ -29972,7 +30018,7 @@
         </is>
       </c>
       <c r="C282" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D282" t="n">
         <v>5</v>
@@ -29999,7 +30045,7 @@
         <v>0</v>
       </c>
       <c r="L282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M282" t="n">
         <v>13</v>
@@ -30017,13 +30063,13 @@
         </is>
       </c>
       <c r="C283" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D283" t="n">
         <v>18</v>
       </c>
       <c r="E283" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F283" t="n">
         <v>2</v>
@@ -30044,7 +30090,7 @@
         <v>10</v>
       </c>
       <c r="L283" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M283" t="n">
         <v>78</v>
@@ -30065,13 +30111,13 @@
         <v>193</v>
       </c>
       <c r="D284" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E284" t="n">
         <v>8</v>
       </c>
       <c r="F284" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G284" t="n">
         <v>13</v>
@@ -30089,7 +30135,7 @@
         <v>13</v>
       </c>
       <c r="L284" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M284" t="n">
         <v>280</v>
@@ -30107,7 +30153,7 @@
         </is>
       </c>
       <c r="C285" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D285" t="n">
         <v>13</v>
@@ -30125,7 +30171,7 @@
         <v>0</v>
       </c>
       <c r="I285" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J285" t="n">
         <v>8</v>
@@ -30134,7 +30180,7 @@
         <v>10</v>
       </c>
       <c r="L285" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M285" t="n">
         <v>101</v>
@@ -30287,13 +30333,13 @@
         </is>
       </c>
       <c r="C289" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D289" t="n">
         <v>18</v>
       </c>
       <c r="E289" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F289" t="n">
         <v>2</v>
@@ -30311,10 +30357,10 @@
         <v>10</v>
       </c>
       <c r="K289" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L289" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M289" t="n">
         <v>88</v>
@@ -30332,13 +30378,13 @@
         </is>
       </c>
       <c r="C290" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D290" t="n">
         <v>17</v>
       </c>
       <c r="E290" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F290" t="n">
         <v>1</v>
@@ -30359,7 +30405,7 @@
         <v>8</v>
       </c>
       <c r="L290" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M290" t="n">
         <v>84</v>
@@ -30938,13 +30984,13 @@
         <v>0</v>
       </c>
       <c r="J303" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K303" t="n">
         <v>6</v>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M303" t="n">
         <v>32</v>
@@ -31007,7 +31053,7 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D305" t="n">
         <v>23</v>
@@ -31034,7 +31080,7 @@
         <v>14</v>
       </c>
       <c r="L305" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M305" t="n">
         <v>95</v>
@@ -31073,13 +31119,13 @@
         <v>1</v>
       </c>
       <c r="J306" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K306" t="n">
         <v>13</v>
       </c>
       <c r="L306" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M306" t="n">
         <v>156</v>
@@ -31097,10 +31143,10 @@
         </is>
       </c>
       <c r="C307" t="n">
+        <v>36</v>
+      </c>
+      <c r="D307" t="n">
         <v>37</v>
-      </c>
-      <c r="D307" t="n">
-        <v>38</v>
       </c>
       <c r="E307" t="n">
         <v>29</v>
@@ -31115,7 +31161,7 @@
         <v>1</v>
       </c>
       <c r="I307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J307" t="n">
         <v>20</v>
@@ -31124,7 +31170,7 @@
         <v>19</v>
       </c>
       <c r="L307" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M307" t="n">
         <v>154</v>
@@ -31145,7 +31191,7 @@
         <v>16</v>
       </c>
       <c r="D308" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E308" t="n">
         <v>7</v>
@@ -31169,7 +31215,7 @@
         <v>14</v>
       </c>
       <c r="L308" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M308" t="n">
         <v>85</v>
@@ -31187,10 +31233,10 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D309" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E309" t="n">
         <v>6</v>
@@ -31214,7 +31260,7 @@
         <v>1</v>
       </c>
       <c r="L309" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M309" t="n">
         <v>37</v>
@@ -31277,7 +31323,7 @@
         </is>
       </c>
       <c r="C311" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D311" t="n">
         <v>8</v>
@@ -31304,7 +31350,7 @@
         <v>3</v>
       </c>
       <c r="L311" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M311" t="n">
         <v>46</v>
@@ -31460,7 +31506,7 @@
         <v>1</v>
       </c>
       <c r="D315" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E315" t="n">
         <v>1</v>
@@ -31484,7 +31530,7 @@
         <v>0</v>
       </c>
       <c r="L315" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M315" t="n">
         <v>9</v>
@@ -31610,7 +31656,7 @@
         <v>0</v>
       </c>
       <c r="I318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J318" t="n">
         <v>2</v>
@@ -31619,7 +31665,7 @@
         <v>1</v>
       </c>
       <c r="L318" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M318" t="n">
         <v>12</v>
@@ -36002,7 +36048,7 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D416" t="n">
         <v>0</v>
@@ -36029,7 +36075,7 @@
         <v>3</v>
       </c>
       <c r="L416" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M416" t="n">
         <v>22</v>
@@ -36146,25 +36192,25 @@
         <v>32</v>
       </c>
       <c r="F419" t="n">
+        <v>9</v>
+      </c>
+      <c r="G419" t="n">
+        <v>2</v>
+      </c>
+      <c r="H419" t="n">
+        <v>2</v>
+      </c>
+      <c r="I419" t="n">
+        <v>2</v>
+      </c>
+      <c r="J419" t="n">
         <v>10</v>
       </c>
-      <c r="G419" t="n">
-        <v>2</v>
-      </c>
-      <c r="H419" t="n">
-        <v>2</v>
-      </c>
-      <c r="I419" t="n">
-        <v>2</v>
-      </c>
-      <c r="J419" t="n">
-        <v>11</v>
-      </c>
       <c r="K419" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L419" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M419" t="n">
         <v>171</v>
@@ -36182,7 +36228,7 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D420" t="n">
         <v>13</v>
@@ -36200,7 +36246,7 @@
         <v>0</v>
       </c>
       <c r="I420" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J420" t="n">
         <v>6</v>
@@ -36209,10 +36255,10 @@
         <v>10</v>
       </c>
       <c r="L420" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M420" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="421">
@@ -36227,7 +36273,7 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D421" t="n">
         <v>13</v>
@@ -36248,13 +36294,13 @@
         <v>1</v>
       </c>
       <c r="J421" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K421" t="n">
         <v>7</v>
       </c>
       <c r="L421" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M421" t="n">
         <v>66</v>
@@ -36317,13 +36363,13 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D423" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E423" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F423" t="n">
         <v>4</v>
@@ -36341,10 +36387,10 @@
         <v>7</v>
       </c>
       <c r="K423" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L423" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M423" t="n">
         <v>66</v>
@@ -36386,10 +36432,10 @@
         <v>4</v>
       </c>
       <c r="K424" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L424" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M424" t="n">
         <v>35</v>
@@ -36542,13 +36588,13 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D428" t="n">
         <v>32</v>
       </c>
       <c r="E428" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F428" t="n">
         <v>2</v>
@@ -36569,7 +36615,7 @@
         <v>16</v>
       </c>
       <c r="L428" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M428" t="n">
         <v>111</v>
@@ -36722,7 +36768,7 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D432" t="n">
         <v>3</v>
@@ -36749,7 +36795,7 @@
         <v>2</v>
       </c>
       <c r="L432" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M432" t="n">
         <v>11</v>
@@ -37130,7 +37176,7 @@
         <v>2</v>
       </c>
       <c r="D441" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E441" t="n">
         <v>1</v>
@@ -37154,7 +37200,7 @@
         <v>1</v>
       </c>
       <c r="L441" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M441" t="n">
         <v>24</v>
@@ -37175,7 +37221,7 @@
         <v>1</v>
       </c>
       <c r="D442" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E442" t="n">
         <v>3</v>
@@ -37199,7 +37245,7 @@
         <v>2</v>
       </c>
       <c r="L442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M442" t="n">
         <v>27</v>
@@ -37397,10 +37443,10 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D447" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E447" t="n">
         <v>5</v>
@@ -37418,13 +37464,13 @@
         <v>1</v>
       </c>
       <c r="J447" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K447" t="n">
         <v>13</v>
       </c>
       <c r="L447" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M447" t="n">
         <v>86</v>
@@ -37463,13 +37509,13 @@
         <v>0</v>
       </c>
       <c r="J448" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K448" t="n">
         <v>8</v>
       </c>
       <c r="L448" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M448" t="n">
         <v>120</v>
@@ -37487,10 +37533,10 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D449" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E449" t="n">
         <v>16</v>
@@ -37508,13 +37554,13 @@
         <v>0</v>
       </c>
       <c r="J449" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K449" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L449" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="M449" t="n">
         <v>110</v>
@@ -37577,7 +37623,7 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D451" t="n">
         <v>9</v>
@@ -37604,7 +37650,7 @@
         <v>0</v>
       </c>
       <c r="L451" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M451" t="n">
         <v>25</v>
@@ -37829,10 +37875,10 @@
         <v>1</v>
       </c>
       <c r="L456" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M456" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="457">
@@ -38006,10 +38052,10 @@
         <v>1</v>
       </c>
       <c r="K460" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L460" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M460" t="n">
         <v>8</v>
@@ -38078,7 +38124,7 @@
         <v>1</v>
       </c>
       <c r="E462" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F462" t="n">
         <v>0</v>
@@ -38102,7 +38148,7 @@
         <v>13</v>
       </c>
       <c r="M462" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="463">
@@ -38213,31 +38259,31 @@
         <v>1</v>
       </c>
       <c r="E465" t="n">
+        <v>3</v>
+      </c>
+      <c r="F465" t="n">
+        <v>2</v>
+      </c>
+      <c r="G465" t="n">
+        <v>1</v>
+      </c>
+      <c r="H465" t="n">
+        <v>0</v>
+      </c>
+      <c r="I465" t="n">
+        <v>0</v>
+      </c>
+      <c r="J465" t="n">
+        <v>1</v>
+      </c>
+      <c r="K465" t="n">
         <v>4</v>
       </c>
-      <c r="F465" t="n">
-        <v>2</v>
-      </c>
-      <c r="G465" t="n">
-        <v>1</v>
-      </c>
-      <c r="H465" t="n">
-        <v>0</v>
-      </c>
-      <c r="I465" t="n">
-        <v>0</v>
-      </c>
-      <c r="J465" t="n">
-        <v>1</v>
-      </c>
-      <c r="K465" t="n">
-        <v>5</v>
-      </c>
       <c r="L465" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M465" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="466">
@@ -42257,7 +42303,7 @@
         </is>
       </c>
       <c r="C555" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D555" t="n">
         <v>2</v>
@@ -42284,7 +42330,7 @@
         <v>3</v>
       </c>
       <c r="L555" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M555" t="n">
         <v>15</v>
@@ -42578,7 +42624,7 @@
         <v>1</v>
       </c>
       <c r="E562" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F562" t="n">
         <v>0</v>
@@ -42599,7 +42645,7 @@
         <v>0</v>
       </c>
       <c r="L562" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M562" t="n">
         <v>6</v>
@@ -42707,7 +42753,7 @@
         </is>
       </c>
       <c r="C565" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D565" t="n">
         <v>0</v>
@@ -42734,7 +42780,7 @@
         <v>0</v>
       </c>
       <c r="L565" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M565" t="n">
         <v>4</v>
@@ -43001,10 +43047,10 @@
         <v>0</v>
       </c>
       <c r="K571" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L571" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M571" t="n">
         <v>1</v>
@@ -43586,10 +43632,10 @@
         <v>1</v>
       </c>
       <c r="K584" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L584" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M584" t="n">
         <v>6</v>
@@ -43610,7 +43656,7 @@
         <v>3</v>
       </c>
       <c r="D585" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E585" t="n">
         <v>0</v>
@@ -43634,7 +43680,7 @@
         <v>2</v>
       </c>
       <c r="L585" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M585" t="n">
         <v>7</v>
@@ -43748,7 +43794,7 @@
         <v>1</v>
       </c>
       <c r="E588" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F588" t="n">
         <v>0</v>
@@ -43769,7 +43815,7 @@
         <v>0</v>
       </c>
       <c r="L588" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M588" t="n">
         <v>6</v>
@@ -45590,7 +45636,7 @@
         <v>2</v>
       </c>
       <c r="D629" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E629" t="n">
         <v>2</v>
@@ -45614,7 +45660,7 @@
         <v>6</v>
       </c>
       <c r="L629" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M629" t="n">
         <v>29</v>
@@ -45815,7 +45861,7 @@
         <v>4</v>
       </c>
       <c r="D634" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E634" t="n">
         <v>0</v>
@@ -45839,7 +45885,7 @@
         <v>6</v>
       </c>
       <c r="L634" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M634" t="n">
         <v>36</v>
@@ -46130,7 +46176,7 @@
         <v>0</v>
       </c>
       <c r="D641" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E641" t="n">
         <v>1</v>
@@ -46154,7 +46200,7 @@
         <v>4</v>
       </c>
       <c r="L641" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M641" t="n">
         <v>19</v>
@@ -46172,7 +46218,7 @@
         </is>
       </c>
       <c r="C642" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D642" t="n">
         <v>9</v>
@@ -46199,7 +46245,7 @@
         <v>3</v>
       </c>
       <c r="L642" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M642" t="n">
         <v>19</v>
@@ -46553,13 +46599,13 @@
         <v>0</v>
       </c>
       <c r="J650" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K650" t="n">
         <v>3</v>
       </c>
       <c r="L650" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M650" t="n">
         <v>26</v>
@@ -47342,7 +47388,7 @@
         </is>
       </c>
       <c r="C668" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D668" t="n">
         <v>14</v>
@@ -47369,7 +47415,7 @@
         <v>15</v>
       </c>
       <c r="L668" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M668" t="n">
         <v>83</v>
@@ -47396,7 +47442,7 @@
         <v>8</v>
       </c>
       <c r="F669" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G669" t="n">
         <v>3</v>
@@ -47408,13 +47454,13 @@
         <v>0</v>
       </c>
       <c r="J669" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K669" t="n">
         <v>10</v>
       </c>
       <c r="L669" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M669" t="n">
         <v>97</v>
@@ -47432,10 +47478,10 @@
         </is>
       </c>
       <c r="C670" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D670" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E670" t="n">
         <v>15</v>
@@ -47450,7 +47496,7 @@
         <v>2</v>
       </c>
       <c r="I670" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J670" t="n">
         <v>11</v>
@@ -47459,7 +47505,7 @@
         <v>8</v>
       </c>
       <c r="L670" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M670" t="n">
         <v>102</v>
@@ -47477,7 +47523,7 @@
         </is>
       </c>
       <c r="C671" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D671" t="n">
         <v>16</v>
@@ -47504,7 +47550,7 @@
         <v>11</v>
       </c>
       <c r="L671" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M671" t="n">
         <v>60</v>
@@ -47522,7 +47568,7 @@
         </is>
       </c>
       <c r="C672" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D672" t="n">
         <v>3</v>
@@ -47549,7 +47595,7 @@
         <v>1</v>
       </c>
       <c r="L672" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M672" t="n">
         <v>25</v>
@@ -47618,7 +47664,7 @@
         <v>6</v>
       </c>
       <c r="E674" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F674" t="n">
         <v>0</v>
@@ -47639,7 +47685,7 @@
         <v>1</v>
       </c>
       <c r="L674" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M674" t="n">
         <v>17</v>
@@ -47945,16 +47991,16 @@
         <v>0</v>
       </c>
       <c r="I681" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J681" t="n">
         <v>0</v>
       </c>
       <c r="K681" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L681" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M681" t="n">
         <v>7</v>
@@ -48176,13 +48222,13 @@
         <v>1</v>
       </c>
       <c r="K686" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L686" t="n">
         <v>0</v>
       </c>
       <c r="M686" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="687">
@@ -49142,7 +49188,7 @@
         </is>
       </c>
       <c r="C708" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D708" t="n">
         <v>3</v>
@@ -49169,7 +49215,7 @@
         <v>0</v>
       </c>
       <c r="L708" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M708" t="n">
         <v>7</v>
@@ -49373,7 +49419,7 @@
         <v>4</v>
       </c>
       <c r="E713" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F713" t="n">
         <v>0</v>
@@ -49394,7 +49440,7 @@
         <v>2</v>
       </c>
       <c r="L713" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M713" t="n">
         <v>10</v>
@@ -51842,7 +51888,7 @@
         </is>
       </c>
       <c r="C768" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D768" t="n">
         <v>0</v>
@@ -51869,7 +51915,7 @@
         <v>0</v>
       </c>
       <c r="L768" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M768" t="n">
         <v>5</v>
@@ -52073,7 +52119,7 @@
         <v>2</v>
       </c>
       <c r="E773" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F773" t="n">
         <v>0</v>
@@ -52094,7 +52140,7 @@
         <v>1</v>
       </c>
       <c r="L773" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M773" t="n">
         <v>6</v>
@@ -52787,7 +52833,7 @@
         </is>
       </c>
       <c r="C789" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D789" t="n">
         <v>8</v>
@@ -52814,7 +52860,7 @@
         <v>1</v>
       </c>
       <c r="L789" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M789" t="n">
         <v>16</v>
@@ -56033,7 +56079,7 @@
         <v>0</v>
       </c>
       <c r="E861" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F861" t="n">
         <v>0</v>
@@ -56054,7 +56100,7 @@
         <v>0</v>
       </c>
       <c r="L861" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M861" t="n">
         <v>1</v>
@@ -57233,22 +57279,22 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>GUTSHIFT</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C888" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D888" t="n">
         <v>0</v>
       </c>
       <c r="E888" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F888" t="n">
         <v>0</v>
@@ -57263,7 +57309,7 @@
         <v>0</v>
       </c>
       <c r="J888" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K888" t="n">
         <v>0</v>
@@ -57272,13 +57318,13 @@
         <v>0</v>
       </c>
       <c r="M888" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
@@ -57287,10 +57333,10 @@
         </is>
       </c>
       <c r="C889" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D889" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E889" t="n">
         <v>0</v>
@@ -57299,7 +57345,7 @@
         <v>0</v>
       </c>
       <c r="G889" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H889" t="n">
         <v>0</v>
@@ -57308,7 +57354,7 @@
         <v>0</v>
       </c>
       <c r="J889" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K889" t="n">
         <v>0</v>
@@ -57317,13 +57363,13 @@
         <v>0</v>
       </c>
       <c r="M889" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
@@ -57335,16 +57381,16 @@
         <v>0</v>
       </c>
       <c r="D890" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E890" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F890" t="n">
         <v>0</v>
       </c>
       <c r="G890" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H890" t="n">
         <v>0</v>
@@ -57362,13 +57408,13 @@
         <v>0</v>
       </c>
       <c r="M890" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
@@ -57377,13 +57423,13 @@
         </is>
       </c>
       <c r="C891" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D891" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E891" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F891" t="n">
         <v>0</v>
@@ -57407,13 +57453,13 @@
         <v>0</v>
       </c>
       <c r="M891" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
@@ -57422,10 +57468,10 @@
         </is>
       </c>
       <c r="C892" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D892" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E892" t="n">
         <v>0</v>
@@ -57434,7 +57480,7 @@
         <v>0</v>
       </c>
       <c r="G892" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H892" t="n">
         <v>0</v>
@@ -57452,13 +57498,13 @@
         <v>0</v>
       </c>
       <c r="M892" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
@@ -57467,7 +57513,7 @@
         </is>
       </c>
       <c r="C893" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D893" t="n">
         <v>0</v>
@@ -57479,7 +57525,7 @@
         <v>0</v>
       </c>
       <c r="G893" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -57503,7 +57549,7 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
@@ -57512,16 +57558,16 @@
         </is>
       </c>
       <c r="C894" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D894" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E894" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F894" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G894" t="n">
         <v>0</v>
@@ -57542,13 +57588,13 @@
         <v>0</v>
       </c>
       <c r="M894" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
@@ -57557,16 +57603,16 @@
         </is>
       </c>
       <c r="C895" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D895" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E895" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F895" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G895" t="n">
         <v>0</v>
@@ -57587,13 +57633,13 @@
         <v>0</v>
       </c>
       <c r="M895" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
@@ -57605,10 +57651,10 @@
         <v>1</v>
       </c>
       <c r="D896" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E896" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F896" t="n">
         <v>0</v>
@@ -57632,13 +57678,13 @@
         <v>0</v>
       </c>
       <c r="M896" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
@@ -57647,13 +57693,13 @@
         </is>
       </c>
       <c r="C897" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D897" t="n">
         <v>1</v>
       </c>
       <c r="E897" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F897" t="n">
         <v>0</v>
@@ -57671,19 +57717,19 @@
         <v>0</v>
       </c>
       <c r="K897" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L897" t="n">
         <v>0</v>
       </c>
       <c r="M897" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
@@ -57713,22 +57759,22 @@
         <v>0</v>
       </c>
       <c r="J898" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K898" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L898" t="n">
         <v>0</v>
       </c>
       <c r="M898" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
@@ -57740,7 +57786,7 @@
         <v>0</v>
       </c>
       <c r="D899" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E899" t="n">
         <v>0</v>
@@ -57758,7 +57804,7 @@
         <v>0</v>
       </c>
       <c r="J899" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K899" t="n">
         <v>0</v>
@@ -57767,13 +57813,13 @@
         <v>0</v>
       </c>
       <c r="M899" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
@@ -57782,10 +57828,10 @@
         </is>
       </c>
       <c r="C900" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D900" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E900" t="n">
         <v>0</v>
@@ -57794,7 +57840,7 @@
         <v>0</v>
       </c>
       <c r="G900" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H900" t="n">
         <v>0</v>
@@ -57806,19 +57852,19 @@
         <v>0</v>
       </c>
       <c r="K900" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L900" t="n">
         <v>0</v>
       </c>
       <c r="M900" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
@@ -57827,10 +57873,10 @@
         </is>
       </c>
       <c r="C901" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D901" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E901" t="n">
         <v>0</v>
@@ -57839,7 +57885,7 @@
         <v>0</v>
       </c>
       <c r="G901" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H901" t="n">
         <v>0</v>
@@ -57851,28 +57897,28 @@
         <v>0</v>
       </c>
       <c r="K901" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L901" t="n">
         <v>0</v>
       </c>
       <c r="M901" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>Matcha</t>
+          <t>GUTSHIFT</t>
         </is>
       </c>
       <c r="C902" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D902" t="n">
         <v>1</v>
@@ -57902,13 +57948,13 @@
         <v>0</v>
       </c>
       <c r="M902" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
@@ -57917,7 +57963,7 @@
         </is>
       </c>
       <c r="C903" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D903" t="n">
         <v>1</v>
@@ -57944,7 +57990,7 @@
         <v>0</v>
       </c>
       <c r="L903" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M903" t="n">
         <v>2</v>
@@ -57953,7 +57999,7 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
@@ -57965,10 +58011,10 @@
         <v>0</v>
       </c>
       <c r="D904" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E904" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F904" t="n">
         <v>0</v>
@@ -57989,16 +58035,16 @@
         <v>0</v>
       </c>
       <c r="L904" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M904" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
@@ -58031,19 +58077,19 @@
         <v>0</v>
       </c>
       <c r="K905" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L905" t="n">
         <v>0</v>
       </c>
       <c r="M905" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
@@ -58052,13 +58098,13 @@
         </is>
       </c>
       <c r="C906" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D906" t="n">
         <v>0</v>
       </c>
       <c r="E906" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F906" t="n">
         <v>0</v>
@@ -58076,19 +58122,19 @@
         <v>0</v>
       </c>
       <c r="K906" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L906" t="n">
         <v>0</v>
       </c>
       <c r="M906" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
@@ -58097,7 +58143,7 @@
         </is>
       </c>
       <c r="C907" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D907" t="n">
         <v>0</v>
@@ -58124,7 +58170,7 @@
         <v>0</v>
       </c>
       <c r="L907" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M907" t="n">
         <v>1</v>
@@ -58133,7 +58179,7 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
@@ -58142,7 +58188,7 @@
         </is>
       </c>
       <c r="C908" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D908" t="n">
         <v>0</v>
@@ -58169,54 +58215,99 @@
         <v>0</v>
       </c>
       <c r="L908" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M908" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Matcha</t>
+        </is>
+      </c>
+      <c r="C909" t="n">
+        <v>2</v>
+      </c>
+      <c r="D909" t="n">
+        <v>0</v>
+      </c>
+      <c r="E909" t="n">
+        <v>0</v>
+      </c>
+      <c r="F909" t="n">
+        <v>0</v>
+      </c>
+      <c r="G909" t="n">
+        <v>0</v>
+      </c>
+      <c r="H909" t="n">
+        <v>0</v>
+      </c>
+      <c r="I909" t="n">
+        <v>0</v>
+      </c>
+      <c r="J909" t="n">
+        <v>0</v>
+      </c>
+      <c r="K909" t="n">
+        <v>0</v>
+      </c>
+      <c r="L909" t="n">
+        <v>0</v>
+      </c>
+      <c r="M909" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
           <t>2026-10-06</t>
         </is>
       </c>
-      <c r="B909" t="inlineStr">
+      <c r="B910" t="inlineStr">
         <is>
           <t>Matcha</t>
         </is>
       </c>
-      <c r="C909" t="n">
-        <v>0</v>
-      </c>
-      <c r="D909" t="n">
-        <v>1</v>
-      </c>
-      <c r="E909" t="n">
-        <v>0</v>
-      </c>
-      <c r="F909" t="n">
-        <v>0</v>
-      </c>
-      <c r="G909" t="n">
-        <v>0</v>
-      </c>
-      <c r="H909" t="n">
-        <v>0</v>
-      </c>
-      <c r="I909" t="n">
-        <v>0</v>
-      </c>
-      <c r="J909" t="n">
-        <v>0</v>
-      </c>
-      <c r="K909" t="n">
-        <v>0</v>
-      </c>
-      <c r="L909" t="n">
-        <v>1</v>
-      </c>
-      <c r="M909" t="n">
+      <c r="C910" t="n">
+        <v>0</v>
+      </c>
+      <c r="D910" t="n">
+        <v>1</v>
+      </c>
+      <c r="E910" t="n">
+        <v>0</v>
+      </c>
+      <c r="F910" t="n">
+        <v>0</v>
+      </c>
+      <c r="G910" t="n">
+        <v>0</v>
+      </c>
+      <c r="H910" t="n">
+        <v>0</v>
+      </c>
+      <c r="I910" t="n">
+        <v>0</v>
+      </c>
+      <c r="J910" t="n">
+        <v>0</v>
+      </c>
+      <c r="K910" t="n">
+        <v>0</v>
+      </c>
+      <c r="L910" t="n">
+        <v>1</v>
+      </c>
+      <c r="M910" t="n">
         <v>2</v>
       </c>
     </row>

--- a/daily_ethnicity_mix.xlsx
+++ b/daily_ethnicity_mix.xlsx
@@ -17838,17 +17838,17 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C379" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D379" t="n">
+        <v>11</v>
+      </c>
+      <c r="E379" t="n">
         <v>5</v>
       </c>
-      <c r="E379" t="n">
-        <v>3</v>
-      </c>
       <c r="F379" t="n">
         <v>1</v>
       </c>
@@ -17856,25 +17856,25 @@
         <v>0</v>
       </c>
       <c r="H379" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I379" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J379" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K379" t="n">
-        <v>53</v>
+        <v>136</v>
       </c>
       <c r="L379" t="n">
-        <v>102</v>
+        <v>234</v>
       </c>
       <c r="M379" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="N379" t="n">
-        <v>37.3</v>
+        <v>34.2</v>
       </c>
     </row>
   </sheetData>
@@ -34575,13 +34575,13 @@
         </is>
       </c>
       <c r="C371" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D371" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E371" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F371" t="n">
         <v>0</v>
@@ -34593,19 +34593,19 @@
         <v>0</v>
       </c>
       <c r="I371" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J371" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K371" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L371" t="n">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="M371" t="n">
-        <v>32</v>
+        <v>99</v>
       </c>
     </row>
     <row r="372">
@@ -41550,16 +41550,16 @@
         </is>
       </c>
       <c r="C526" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D526" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E526" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F526" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G526" t="n">
         <v>0</v>
@@ -41571,16 +41571,16 @@
         <v>0</v>
       </c>
       <c r="J526" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K526" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L526" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="M526" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="527">
@@ -47808,13 +47808,13 @@
         <v>0</v>
       </c>
       <c r="D665" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E665" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F665" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G665" t="n">
         <v>0</v>
@@ -47832,10 +47832,10 @@
         <v>0</v>
       </c>
       <c r="L665" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M665" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="666">
@@ -49968,10 +49968,10 @@
         <v>0</v>
       </c>
       <c r="D713" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E713" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F713" t="n">
         <v>1</v>
@@ -49992,10 +49992,10 @@
         <v>0</v>
       </c>
       <c r="L713" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M713" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="714">
@@ -53205,10 +53205,10 @@
         </is>
       </c>
       <c r="C785" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D785" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E785" t="n">
         <v>1</v>
@@ -53232,10 +53232,10 @@
         <v>2</v>
       </c>
       <c r="L785" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="M785" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="786">
@@ -56355,10 +56355,10 @@
         </is>
       </c>
       <c r="C855" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D855" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E855" t="n">
         <v>2</v>
@@ -56382,10 +56382,10 @@
         <v>3</v>
       </c>
       <c r="L855" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="M855" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
     </row>
     <row r="856">
@@ -59847,10 +59847,10 @@
         <v>0</v>
       </c>
       <c r="L932" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M932" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="933">

--- a/daily_ethnicity_mix.xlsx
+++ b/daily_ethnicity_mix.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2613" uniqueCount="411">
   <si>
     <t>Date</t>
   </si>
@@ -18333,43 +18333,43 @@
         <v>393</v>
       </c>
       <c r="B381">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="C381">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D381">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E381">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F381">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G381">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H381">
         <v>0</v>
       </c>
       <c r="I381">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J381">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K381">
-        <v>56</v>
+        <v>144</v>
       </c>
       <c r="L381">
-        <v>103</v>
+        <v>275</v>
       </c>
       <c r="M381">
-        <v>34</v>
+        <v>101</v>
       </c>
       <c r="N381">
-        <v>33</v>
+        <v>36.7</v>
       </c>
     </row>
   </sheetData>
@@ -18379,7 +18379,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M1101"/>
+  <dimension ref="A1:M1104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:13">
@@ -33519,37 +33519,37 @@
         <v>395</v>
       </c>
       <c r="C370">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D370">
+        <v>13</v>
+      </c>
+      <c r="E370">
+        <v>3</v>
+      </c>
+      <c r="F370">
+        <v>0</v>
+      </c>
+      <c r="G370">
+        <v>3</v>
+      </c>
+      <c r="H370">
+        <v>0</v>
+      </c>
+      <c r="I370">
+        <v>0</v>
+      </c>
+      <c r="J370">
         <v>9</v>
       </c>
-      <c r="E370">
-        <v>1</v>
-      </c>
-      <c r="F370">
-        <v>0</v>
-      </c>
-      <c r="G370">
-        <v>1</v>
-      </c>
-      <c r="H370">
-        <v>0</v>
-      </c>
-      <c r="I370">
-        <v>0</v>
-      </c>
-      <c r="J370">
-        <v>5</v>
-      </c>
       <c r="K370">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L370">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="M370">
-        <v>45</v>
+        <v>106</v>
       </c>
     </row>
     <row r="371" spans="1:13">
@@ -39956,13 +39956,13 @@
         <v>396</v>
       </c>
       <c r="C527">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D527">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E527">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F527">
         <v>0</v>
@@ -39977,16 +39977,16 @@
         <v>0</v>
       </c>
       <c r="J527">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K527">
         <v>2</v>
       </c>
       <c r="L527">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="M527">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="528" spans="1:13">
@@ -45737,13 +45737,13 @@
         <v>397</v>
       </c>
       <c r="C668">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D668">
         <v>1</v>
       </c>
       <c r="E668">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F668">
         <v>0</v>
@@ -45764,10 +45764,10 @@
         <v>1</v>
       </c>
       <c r="L668">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M668">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="669" spans="1:13">
@@ -48361,10 +48361,10 @@
         <v>398</v>
       </c>
       <c r="C732">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D732">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E732">
         <v>1</v>
@@ -48382,16 +48382,16 @@
         <v>0</v>
       </c>
       <c r="J732">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K732">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L732">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M732">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="733" spans="1:13">
@@ -51108,10 +51108,10 @@
         <v>400</v>
       </c>
       <c r="C799">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D799">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E799">
         <v>0</v>
@@ -51120,7 +51120,7 @@
         <v>1</v>
       </c>
       <c r="G799">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H799">
         <v>0</v>
@@ -51132,13 +51132,13 @@
         <v>2</v>
       </c>
       <c r="K799">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L799">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="M799">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="800" spans="1:13">
@@ -51641,37 +51641,37 @@
         <v>401</v>
       </c>
       <c r="C812">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="D812">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E812">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F812">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G812">
         <v>0</v>
       </c>
       <c r="H812">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I812">
         <v>0</v>
       </c>
       <c r="J812">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K812">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L812">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="M812">
-        <v>12</v>
+        <v>100</v>
       </c>
     </row>
     <row r="813" spans="1:13">
@@ -54883,10 +54883,10 @@
         <v>0</v>
       </c>
       <c r="D891">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E891">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F891">
         <v>0</v>
@@ -54910,7 +54910,7 @@
         <v>3</v>
       </c>
       <c r="M891">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="892" spans="1:13">
@@ -57170,16 +57170,16 @@
     </row>
     <row r="947" spans="1:13">
       <c r="A947" t="s">
-        <v>133</v>
+        <v>393</v>
       </c>
       <c r="B947" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C947">
         <v>0</v>
       </c>
       <c r="D947">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E947">
         <v>0</v>
@@ -57188,7 +57188,7 @@
         <v>0</v>
       </c>
       <c r="G947">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H947">
         <v>0</v>
@@ -57197,7 +57197,7 @@
         <v>0</v>
       </c>
       <c r="J947">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K947">
         <v>0</v>
@@ -57206,18 +57206,18 @@
         <v>0</v>
       </c>
       <c r="M947">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="948" spans="1:13">
       <c r="A948" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B948" t="s">
         <v>404</v>
       </c>
       <c r="C948">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D948">
         <v>0</v>
@@ -57229,7 +57229,7 @@
         <v>0</v>
       </c>
       <c r="G948">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H948">
         <v>0</v>
@@ -57252,7 +57252,7 @@
     </row>
     <row r="949" spans="1:13">
       <c r="A949" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B949" t="s">
         <v>404</v>
@@ -57279,7 +57279,7 @@
         <v>0</v>
       </c>
       <c r="J949">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K949">
         <v>0</v>
@@ -57288,18 +57288,18 @@
         <v>0</v>
       </c>
       <c r="M949">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="950" spans="1:13">
       <c r="A950" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="B950" t="s">
         <v>404</v>
       </c>
       <c r="C950">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D950">
         <v>0</v>
@@ -57308,7 +57308,7 @@
         <v>0</v>
       </c>
       <c r="F950">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G950">
         <v>0</v>
@@ -57334,13 +57334,13 @@
     </row>
     <row r="951" spans="1:13">
       <c r="A951" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B951" t="s">
         <v>404</v>
       </c>
       <c r="C951">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D951">
         <v>0</v>
@@ -57349,7 +57349,7 @@
         <v>0</v>
       </c>
       <c r="F951">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G951">
         <v>0</v>
@@ -57370,21 +57370,21 @@
         <v>0</v>
       </c>
       <c r="M951">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="952" spans="1:13">
       <c r="A952" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B952" t="s">
         <v>404</v>
       </c>
       <c r="C952">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D952">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E952">
         <v>0</v>
@@ -57405,30 +57405,30 @@
         <v>0</v>
       </c>
       <c r="K952">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L952">
         <v>0</v>
       </c>
       <c r="M952">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="953" spans="1:13">
       <c r="A953" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B953" t="s">
         <v>404</v>
       </c>
       <c r="C953">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D953">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E953">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F953">
         <v>0</v>
@@ -57443,7 +57443,7 @@
         <v>0</v>
       </c>
       <c r="J953">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K953">
         <v>1</v>
@@ -57452,24 +57452,24 @@
         <v>0</v>
       </c>
       <c r="M953">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="954" spans="1:13">
       <c r="A954" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B954" t="s">
         <v>404</v>
       </c>
       <c r="C954">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D954">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E954">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F954">
         <v>0</v>
@@ -57481,30 +57481,30 @@
         <v>0</v>
       </c>
       <c r="I954">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J954">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K954">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L954">
         <v>0</v>
       </c>
       <c r="M954">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="955" spans="1:13">
       <c r="A955" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B955" t="s">
         <v>404</v>
       </c>
       <c r="C955">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D955">
         <v>0</v>
@@ -57522,30 +57522,30 @@
         <v>0</v>
       </c>
       <c r="I955">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J955">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K955">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L955">
         <v>0</v>
       </c>
       <c r="M955">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="956" spans="1:13">
       <c r="A956" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B956" t="s">
         <v>404</v>
       </c>
       <c r="C956">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D956">
         <v>0</v>
@@ -57566,21 +57566,21 @@
         <v>0</v>
       </c>
       <c r="J956">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K956">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L956">
         <v>0</v>
       </c>
       <c r="M956">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="957" spans="1:13">
       <c r="A957" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B957" t="s">
         <v>404</v>
@@ -57607,7 +57607,7 @@
         <v>0</v>
       </c>
       <c r="J957">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K957">
         <v>0</v>
@@ -57616,18 +57616,18 @@
         <v>0</v>
       </c>
       <c r="M957">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="958" spans="1:13">
       <c r="A958" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B958" t="s">
         <v>404</v>
       </c>
       <c r="C958">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D958">
         <v>0</v>
@@ -57648,10 +57648,10 @@
         <v>0</v>
       </c>
       <c r="J958">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K958">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L958">
         <v>0</v>
@@ -57662,19 +57662,19 @@
     </row>
     <row r="959" spans="1:13">
       <c r="A959" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B959" t="s">
         <v>404</v>
       </c>
       <c r="C959">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D959">
         <v>0</v>
       </c>
       <c r="E959">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F959">
         <v>0</v>
@@ -57689,33 +57689,33 @@
         <v>0</v>
       </c>
       <c r="J959">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K959">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L959">
         <v>0</v>
       </c>
       <c r="M959">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="960" spans="1:13">
       <c r="A960" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B960" t="s">
         <v>404</v>
       </c>
       <c r="C960">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D960">
         <v>0</v>
       </c>
       <c r="E960">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F960">
         <v>0</v>
@@ -57733,18 +57733,18 @@
         <v>0</v>
       </c>
       <c r="K960">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L960">
         <v>0</v>
       </c>
       <c r="M960">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="961" spans="1:13">
       <c r="A961" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B961" t="s">
         <v>404</v>
@@ -57753,7 +57753,7 @@
         <v>0</v>
       </c>
       <c r="D961">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E961">
         <v>0</v>
@@ -57774,7 +57774,7 @@
         <v>0</v>
       </c>
       <c r="K961">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L961">
         <v>0</v>
@@ -57785,7 +57785,7 @@
     </row>
     <row r="962" spans="1:13">
       <c r="A962" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B962" t="s">
         <v>404</v>
@@ -57826,7 +57826,7 @@
     </row>
     <row r="963" spans="1:13">
       <c r="A963" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B963" t="s">
         <v>404</v>
@@ -57841,7 +57841,7 @@
         <v>0</v>
       </c>
       <c r="F963">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G963">
         <v>0</v>
@@ -57862,27 +57862,27 @@
         <v>0</v>
       </c>
       <c r="M963">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="964" spans="1:13">
       <c r="A964" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B964" t="s">
         <v>404</v>
       </c>
       <c r="C964">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D964">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E964">
         <v>0</v>
       </c>
       <c r="F964">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G964">
         <v>0</v>
@@ -57891,7 +57891,7 @@
         <v>0</v>
       </c>
       <c r="I964">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J964">
         <v>0</v>
@@ -57908,7 +57908,7 @@
     </row>
     <row r="965" spans="1:13">
       <c r="A965" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B965" t="s">
         <v>404</v>
@@ -57932,13 +57932,13 @@
         <v>0</v>
       </c>
       <c r="I965">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J965">
         <v>0</v>
       </c>
       <c r="K965">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L965">
         <v>0</v>
@@ -57949,7 +57949,7 @@
     </row>
     <row r="966" spans="1:13">
       <c r="A966" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B966" t="s">
         <v>404</v>
@@ -57990,13 +57990,13 @@
     </row>
     <row r="967" spans="1:13">
       <c r="A967" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B967" t="s">
         <v>404</v>
       </c>
       <c r="C967">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D967">
         <v>0</v>
@@ -58020,18 +58020,18 @@
         <v>0</v>
       </c>
       <c r="K967">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L967">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M967">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="968" spans="1:13">
       <c r="A968" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B968" t="s">
         <v>404</v>
@@ -58058,13 +58058,13 @@
         <v>0</v>
       </c>
       <c r="J968">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K968">
         <v>0</v>
       </c>
       <c r="L968">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M968">
         <v>1</v>
@@ -58072,13 +58072,13 @@
     </row>
     <row r="969" spans="1:13">
       <c r="A969" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="B969" t="s">
         <v>404</v>
       </c>
       <c r="C969">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D969">
         <v>0</v>
@@ -58099,7 +58099,7 @@
         <v>0</v>
       </c>
       <c r="J969">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K969">
         <v>0</v>
@@ -58113,13 +58113,13 @@
     </row>
     <row r="970" spans="1:13">
       <c r="A970" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B970" t="s">
         <v>404</v>
       </c>
       <c r="C970">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D970">
         <v>0</v>
@@ -58149,21 +58149,21 @@
         <v>0</v>
       </c>
       <c r="M970">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="971" spans="1:13">
       <c r="A971" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B971" t="s">
         <v>404</v>
       </c>
       <c r="C971">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D971">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E971">
         <v>0</v>
@@ -58184,18 +58184,18 @@
         <v>0</v>
       </c>
       <c r="K971">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L971">
         <v>0</v>
       </c>
       <c r="M971">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="972" spans="1:13">
       <c r="A972" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B972" t="s">
         <v>404</v>
@@ -58204,7 +58204,7 @@
         <v>1</v>
       </c>
       <c r="D972">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E972">
         <v>0</v>
@@ -58225,24 +58225,24 @@
         <v>0</v>
       </c>
       <c r="K972">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L972">
         <v>0</v>
       </c>
       <c r="M972">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="973" spans="1:13">
       <c r="A973" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B973" t="s">
         <v>404</v>
       </c>
       <c r="C973">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D973">
         <v>0</v>
@@ -58263,7 +58263,7 @@
         <v>0</v>
       </c>
       <c r="J973">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K973">
         <v>0</v>
@@ -58272,18 +58272,18 @@
         <v>0</v>
       </c>
       <c r="M973">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="974" spans="1:13">
       <c r="A974" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B974" t="s">
         <v>404</v>
       </c>
       <c r="C974">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D974">
         <v>0</v>
@@ -58304,21 +58304,21 @@
         <v>0</v>
       </c>
       <c r="J974">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K974">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L974">
         <v>0</v>
       </c>
       <c r="M974">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="975" spans="1:13">
       <c r="A975" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="B975" t="s">
         <v>404</v>
@@ -58348,24 +58348,24 @@
         <v>0</v>
       </c>
       <c r="K975">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L975">
         <v>0</v>
       </c>
       <c r="M975">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="976" spans="1:13">
       <c r="A976" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B976" t="s">
         <v>404</v>
       </c>
       <c r="C976">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D976">
         <v>0</v>
@@ -58395,18 +58395,18 @@
         <v>0</v>
       </c>
       <c r="M976">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="977" spans="1:13">
       <c r="A977" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B977" t="s">
         <v>404</v>
       </c>
       <c r="C977">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D977">
         <v>0</v>
@@ -58436,12 +58436,12 @@
         <v>0</v>
       </c>
       <c r="M977">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="978" spans="1:13">
       <c r="A978" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="B978" t="s">
         <v>404</v>
@@ -58482,13 +58482,13 @@
     </row>
     <row r="979" spans="1:13">
       <c r="A979" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B979" t="s">
         <v>404</v>
       </c>
       <c r="C979">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D979">
         <v>0</v>
@@ -58497,7 +58497,7 @@
         <v>0</v>
       </c>
       <c r="F979">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G979">
         <v>0</v>
@@ -58523,13 +58523,13 @@
     </row>
     <row r="980" spans="1:13">
       <c r="A980" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="B980" t="s">
         <v>404</v>
       </c>
       <c r="C980">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D980">
         <v>0</v>
@@ -58538,7 +58538,7 @@
         <v>0</v>
       </c>
       <c r="F980">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G980">
         <v>0</v>
@@ -58550,7 +58550,7 @@
         <v>0</v>
       </c>
       <c r="J980">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K980">
         <v>0</v>
@@ -58559,18 +58559,18 @@
         <v>0</v>
       </c>
       <c r="M980">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="981" spans="1:13">
       <c r="A981" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B981" t="s">
         <v>404</v>
       </c>
       <c r="C981">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D981">
         <v>0</v>
@@ -58591,7 +58591,7 @@
         <v>0</v>
       </c>
       <c r="J981">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K981">
         <v>0</v>
@@ -58605,13 +58605,13 @@
     </row>
     <row r="982" spans="1:13">
       <c r="A982" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="B982" t="s">
         <v>404</v>
       </c>
       <c r="C982">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D982">
         <v>0</v>
@@ -58635,18 +58635,18 @@
         <v>0</v>
       </c>
       <c r="K982">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L982">
         <v>0</v>
       </c>
       <c r="M982">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="983" spans="1:13">
       <c r="A983" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B983" t="s">
         <v>404</v>
@@ -58658,7 +58658,7 @@
         <v>0</v>
       </c>
       <c r="E983">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F983">
         <v>0</v>
@@ -58676,7 +58676,7 @@
         <v>0</v>
       </c>
       <c r="K983">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L983">
         <v>0</v>
@@ -58687,19 +58687,19 @@
     </row>
     <row r="984" spans="1:13">
       <c r="A984" t="s">
-        <v>294</v>
+        <v>259</v>
       </c>
       <c r="B984" t="s">
         <v>404</v>
       </c>
       <c r="C984">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D984">
         <v>0</v>
       </c>
       <c r="E984">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F984">
         <v>0</v>
@@ -58728,22 +58728,22 @@
     </row>
     <row r="985" spans="1:13">
       <c r="A985" t="s">
-        <v>234</v>
+        <v>294</v>
       </c>
       <c r="B985" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C985">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D985">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E985">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F985">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G985">
         <v>0</v>
@@ -58755,21 +58755,21 @@
         <v>0</v>
       </c>
       <c r="J985">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K985">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L985">
         <v>0</v>
       </c>
       <c r="M985">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="986" spans="1:13">
       <c r="A986" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B986" t="s">
         <v>405</v>
@@ -58778,13 +58778,13 @@
         <v>0</v>
       </c>
       <c r="D986">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E986">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F986">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G986">
         <v>0</v>
@@ -58796,27 +58796,27 @@
         <v>0</v>
       </c>
       <c r="J986">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K986">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L986">
         <v>0</v>
       </c>
       <c r="M986">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="987" spans="1:13">
       <c r="A987" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B987" t="s">
         <v>405</v>
       </c>
       <c r="C987">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D987">
         <v>0</v>
@@ -58825,7 +58825,7 @@
         <v>0</v>
       </c>
       <c r="F987">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G987">
         <v>0</v>
@@ -58851,16 +58851,16 @@
     </row>
     <row r="988" spans="1:13">
       <c r="A988" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B988" t="s">
         <v>405</v>
       </c>
       <c r="C988">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D988">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E988">
         <v>0</v>
@@ -58892,7 +58892,7 @@
     </row>
     <row r="989" spans="1:13">
       <c r="A989" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="B989" t="s">
         <v>405</v>
@@ -58901,7 +58901,7 @@
         <v>0</v>
       </c>
       <c r="D989">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E989">
         <v>0</v>
@@ -58928,12 +58928,12 @@
         <v>0</v>
       </c>
       <c r="M989">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="990" spans="1:13">
       <c r="A990" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B990" t="s">
         <v>405</v>
@@ -58942,7 +58942,7 @@
         <v>0</v>
       </c>
       <c r="D990">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E990">
         <v>0</v>
@@ -58963,18 +58963,18 @@
         <v>0</v>
       </c>
       <c r="K990">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L990">
         <v>0</v>
       </c>
       <c r="M990">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="991" spans="1:13">
       <c r="A991" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B991" t="s">
         <v>405</v>
@@ -58983,7 +58983,7 @@
         <v>0</v>
       </c>
       <c r="D991">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E991">
         <v>0</v>
@@ -59004,7 +59004,7 @@
         <v>0</v>
       </c>
       <c r="K991">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L991">
         <v>0</v>
@@ -59015,7 +59015,7 @@
     </row>
     <row r="992" spans="1:13">
       <c r="A992" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B992" t="s">
         <v>405</v>
@@ -59056,16 +59056,16 @@
     </row>
     <row r="993" spans="1:13">
       <c r="A993" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B993" t="s">
         <v>405</v>
       </c>
       <c r="C993">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D993">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E993">
         <v>0</v>
@@ -59097,16 +59097,16 @@
     </row>
     <row r="994" spans="1:13">
       <c r="A994" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B994" t="s">
         <v>405</v>
       </c>
       <c r="C994">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D994">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E994">
         <v>0</v>
@@ -59138,7 +59138,7 @@
     </row>
     <row r="995" spans="1:13">
       <c r="A995" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B995" t="s">
         <v>405</v>
@@ -59147,10 +59147,10 @@
         <v>0</v>
       </c>
       <c r="D995">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E995">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F995">
         <v>0</v>
@@ -59174,12 +59174,12 @@
         <v>0</v>
       </c>
       <c r="M995">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="996" spans="1:13">
       <c r="A996" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B996" t="s">
         <v>405</v>
@@ -59188,7 +59188,7 @@
         <v>0</v>
       </c>
       <c r="D996">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E996">
         <v>1</v>
@@ -59215,12 +59215,12 @@
         <v>0</v>
       </c>
       <c r="M996">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="997" spans="1:13">
       <c r="A997" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B997" t="s">
         <v>405</v>
@@ -59261,7 +59261,7 @@
     </row>
     <row r="998" spans="1:13">
       <c r="A998" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B998" t="s">
         <v>405</v>
@@ -59273,7 +59273,7 @@
         <v>0</v>
       </c>
       <c r="E998">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F998">
         <v>0</v>
@@ -59291,7 +59291,7 @@
         <v>0</v>
       </c>
       <c r="K998">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L998">
         <v>0</v>
@@ -59302,7 +59302,7 @@
     </row>
     <row r="999" spans="1:13">
       <c r="A999" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B999" t="s">
         <v>405</v>
@@ -59311,7 +59311,7 @@
         <v>0</v>
       </c>
       <c r="D999">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E999">
         <v>0</v>
@@ -59332,7 +59332,7 @@
         <v>0</v>
       </c>
       <c r="K999">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L999">
         <v>0</v>
@@ -59343,7 +59343,7 @@
     </row>
     <row r="1000" spans="1:13">
       <c r="A1000" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B1000" t="s">
         <v>405</v>
@@ -59384,7 +59384,7 @@
     </row>
     <row r="1001" spans="1:13">
       <c r="A1001" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B1001" t="s">
         <v>405</v>
@@ -59425,7 +59425,7 @@
     </row>
     <row r="1002" spans="1:13">
       <c r="A1002" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B1002" t="s">
         <v>405</v>
@@ -59466,7 +59466,7 @@
     </row>
     <row r="1003" spans="1:13">
       <c r="A1003" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B1003" t="s">
         <v>405</v>
@@ -59481,7 +59481,7 @@
         <v>0</v>
       </c>
       <c r="F1003">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1003">
         <v>0</v>
@@ -59502,12 +59502,12 @@
         <v>0</v>
       </c>
       <c r="M1003">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1004" spans="1:13">
       <c r="A1004" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B1004" t="s">
         <v>405</v>
@@ -59516,13 +59516,13 @@
         <v>0</v>
       </c>
       <c r="D1004">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1004">
         <v>0</v>
       </c>
       <c r="F1004">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1004">
         <v>0</v>
@@ -59534,7 +59534,7 @@
         <v>0</v>
       </c>
       <c r="J1004">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1004">
         <v>0</v>
@@ -59543,12 +59543,12 @@
         <v>0</v>
       </c>
       <c r="M1004">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1005" spans="1:13">
       <c r="A1005" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B1005" t="s">
         <v>405</v>
@@ -59578,18 +59578,18 @@
         <v>1</v>
       </c>
       <c r="K1005">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1005">
         <v>0</v>
       </c>
       <c r="M1005">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1006" spans="1:13">
       <c r="A1006" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B1006" t="s">
         <v>405</v>
@@ -59616,10 +59616,10 @@
         <v>0</v>
       </c>
       <c r="J1006">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K1006">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1006">
         <v>0</v>
@@ -59630,7 +59630,7 @@
     </row>
     <row r="1007" spans="1:13">
       <c r="A1007" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B1007" t="s">
         <v>405</v>
@@ -59639,7 +59639,7 @@
         <v>0</v>
       </c>
       <c r="D1007">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1007">
         <v>0</v>
@@ -59657,7 +59657,7 @@
         <v>0</v>
       </c>
       <c r="J1007">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K1007">
         <v>0</v>
@@ -59666,12 +59666,12 @@
         <v>0</v>
       </c>
       <c r="M1007">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1008" spans="1:13">
       <c r="A1008" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B1008" t="s">
         <v>405</v>
@@ -59680,7 +59680,7 @@
         <v>0</v>
       </c>
       <c r="D1008">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1008">
         <v>0</v>
@@ -59698,7 +59698,7 @@
         <v>0</v>
       </c>
       <c r="J1008">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1008">
         <v>0</v>
@@ -59712,7 +59712,7 @@
     </row>
     <row r="1009" spans="1:13">
       <c r="A1009" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B1009" t="s">
         <v>405</v>
@@ -59721,7 +59721,7 @@
         <v>0</v>
       </c>
       <c r="D1009">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1009">
         <v>0</v>
@@ -59739,7 +59739,7 @@
         <v>0</v>
       </c>
       <c r="J1009">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1009">
         <v>0</v>
@@ -59753,13 +59753,13 @@
     </row>
     <row r="1010" spans="1:13">
       <c r="A1010" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B1010" t="s">
         <v>405</v>
       </c>
       <c r="C1010">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1010">
         <v>1</v>
@@ -59783,27 +59783,27 @@
         <v>0</v>
       </c>
       <c r="K1010">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1010">
         <v>0</v>
       </c>
       <c r="M1010">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1011" spans="1:13">
       <c r="A1011" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B1011" t="s">
         <v>405</v>
       </c>
       <c r="C1011">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1011">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1011">
         <v>0</v>
@@ -59830,12 +59830,12 @@
         <v>0</v>
       </c>
       <c r="M1011">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1012" spans="1:13">
       <c r="A1012" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B1012" t="s">
         <v>405</v>
@@ -59876,7 +59876,7 @@
     </row>
     <row r="1013" spans="1:13">
       <c r="A1013" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B1013" t="s">
         <v>405</v>
@@ -59885,7 +59885,7 @@
         <v>0</v>
       </c>
       <c r="D1013">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1013">
         <v>0</v>
@@ -59906,7 +59906,7 @@
         <v>0</v>
       </c>
       <c r="K1013">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1013">
         <v>0</v>
@@ -59917,7 +59917,7 @@
     </row>
     <row r="1014" spans="1:13">
       <c r="A1014" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B1014" t="s">
         <v>405</v>
@@ -59926,10 +59926,10 @@
         <v>0</v>
       </c>
       <c r="D1014">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1014">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1014">
         <v>0</v>
@@ -59958,7 +59958,7 @@
     </row>
     <row r="1015" spans="1:13">
       <c r="A1015" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B1015" t="s">
         <v>405</v>
@@ -59970,7 +59970,7 @@
         <v>0</v>
       </c>
       <c r="E1015">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1015">
         <v>0</v>
@@ -59988,7 +59988,7 @@
         <v>0</v>
       </c>
       <c r="K1015">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1015">
         <v>0</v>
@@ -59999,7 +59999,7 @@
     </row>
     <row r="1016" spans="1:13">
       <c r="A1016" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B1016" t="s">
         <v>405</v>
@@ -60040,7 +60040,7 @@
     </row>
     <row r="1017" spans="1:13">
       <c r="A1017" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B1017" t="s">
         <v>405</v>
@@ -60049,7 +60049,7 @@
         <v>0</v>
       </c>
       <c r="D1017">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1017">
         <v>0</v>
@@ -60070,7 +60070,7 @@
         <v>0</v>
       </c>
       <c r="K1017">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1017">
         <v>0</v>
@@ -60081,7 +60081,7 @@
     </row>
     <row r="1018" spans="1:13">
       <c r="A1018" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B1018" t="s">
         <v>405</v>
@@ -60090,10 +60090,10 @@
         <v>0</v>
       </c>
       <c r="D1018">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1018">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1018">
         <v>0</v>
@@ -60122,7 +60122,7 @@
     </row>
     <row r="1019" spans="1:13">
       <c r="A1019" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B1019" t="s">
         <v>405</v>
@@ -60134,7 +60134,7 @@
         <v>0</v>
       </c>
       <c r="E1019">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1019">
         <v>0</v>
@@ -60149,7 +60149,7 @@
         <v>0</v>
       </c>
       <c r="J1019">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1019">
         <v>0</v>
@@ -60163,7 +60163,7 @@
     </row>
     <row r="1020" spans="1:13">
       <c r="A1020" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B1020" t="s">
         <v>405</v>
@@ -60204,7 +60204,7 @@
     </row>
     <row r="1021" spans="1:13">
       <c r="A1021" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B1021" t="s">
         <v>405</v>
@@ -60213,7 +60213,7 @@
         <v>0</v>
       </c>
       <c r="D1021">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1021">
         <v>0</v>
@@ -60240,12 +60240,12 @@
         <v>0</v>
       </c>
       <c r="M1021">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1022" spans="1:13">
       <c r="A1022" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B1022" t="s">
         <v>405</v>
@@ -60272,7 +60272,7 @@
         <v>0</v>
       </c>
       <c r="J1022">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1022">
         <v>0</v>
@@ -60281,12 +60281,12 @@
         <v>0</v>
       </c>
       <c r="M1022">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1023" spans="1:13">
       <c r="A1023" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B1023" t="s">
         <v>405</v>
@@ -60313,21 +60313,21 @@
         <v>0</v>
       </c>
       <c r="J1023">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1023">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1023">
         <v>0</v>
       </c>
       <c r="M1023">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1024" spans="1:13">
       <c r="A1024" t="s">
-        <v>354</v>
+        <v>315</v>
       </c>
       <c r="B1024" t="s">
         <v>405</v>
@@ -60336,7 +60336,7 @@
         <v>0</v>
       </c>
       <c r="D1024">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1024">
         <v>0</v>
@@ -60354,21 +60354,21 @@
         <v>0</v>
       </c>
       <c r="J1024">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1024">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1024">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1024">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1025" spans="1:13">
       <c r="A1025" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B1025" t="s">
         <v>405</v>
@@ -60377,7 +60377,7 @@
         <v>0</v>
       </c>
       <c r="D1025">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1025">
         <v>0</v>
@@ -60395,7 +60395,7 @@
         <v>0</v>
       </c>
       <c r="J1025">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1025">
         <v>0</v>
@@ -60404,21 +60404,21 @@
         <v>1</v>
       </c>
       <c r="M1025">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1026" spans="1:13">
       <c r="A1026" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B1026" t="s">
         <v>405</v>
       </c>
       <c r="C1026">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1026">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1026">
         <v>0</v>
@@ -60439,18 +60439,18 @@
         <v>1</v>
       </c>
       <c r="K1026">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1026">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M1026">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1027" spans="1:13">
       <c r="A1027" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B1027" t="s">
         <v>405</v>
@@ -60477,27 +60477,27 @@
         <v>0</v>
       </c>
       <c r="J1027">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1027">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1027">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M1027">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1028" spans="1:13">
       <c r="A1028" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B1028" t="s">
         <v>405</v>
       </c>
       <c r="C1028">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1028">
         <v>0</v>
@@ -60524,7 +60524,7 @@
         <v>0</v>
       </c>
       <c r="L1028">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1028">
         <v>1</v>
@@ -60532,7 +60532,7 @@
     </row>
     <row r="1029" spans="1:13">
       <c r="A1029" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B1029" t="s">
         <v>405</v>
@@ -60573,13 +60573,13 @@
     </row>
     <row r="1030" spans="1:13">
       <c r="A1030" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B1030" t="s">
         <v>405</v>
       </c>
       <c r="C1030">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1030">
         <v>0</v>
@@ -60603,18 +60603,18 @@
         <v>0</v>
       </c>
       <c r="K1030">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1030">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1030">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1031" spans="1:13">
       <c r="A1031" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B1031" t="s">
         <v>405</v>
@@ -60644,24 +60644,24 @@
         <v>0</v>
       </c>
       <c r="K1031">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1031">
         <v>0</v>
       </c>
       <c r="M1031">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1032" spans="1:13">
       <c r="A1032" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B1032" t="s">
         <v>405</v>
       </c>
       <c r="C1032">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1032">
         <v>0</v>
@@ -60688,7 +60688,7 @@
         <v>0</v>
       </c>
       <c r="L1032">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1032">
         <v>1</v>
@@ -60696,7 +60696,7 @@
     </row>
     <row r="1033" spans="1:13">
       <c r="A1033" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B1033" t="s">
         <v>405</v>
@@ -60714,7 +60714,7 @@
         <v>0</v>
       </c>
       <c r="G1033">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1033">
         <v>0</v>
@@ -60729,7 +60729,7 @@
         <v>0</v>
       </c>
       <c r="L1033">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1033">
         <v>1</v>
@@ -60737,7 +60737,7 @@
     </row>
     <row r="1034" spans="1:13">
       <c r="A1034" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B1034" t="s">
         <v>405</v>
@@ -60755,7 +60755,7 @@
         <v>0</v>
       </c>
       <c r="G1034">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1034">
         <v>0</v>
@@ -60770,7 +60770,7 @@
         <v>0</v>
       </c>
       <c r="L1034">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1034">
         <v>1</v>
@@ -60778,16 +60778,16 @@
     </row>
     <row r="1035" spans="1:13">
       <c r="A1035" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="B1035" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C1035">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1035">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1035">
         <v>0</v>
@@ -60811,15 +60811,15 @@
         <v>0</v>
       </c>
       <c r="L1035">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1035">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1036" spans="1:13">
       <c r="A1036" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B1036" t="s">
         <v>406</v>
@@ -60849,18 +60849,18 @@
         <v>0</v>
       </c>
       <c r="K1036">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1036">
         <v>0</v>
       </c>
       <c r="M1036">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1037" spans="1:13">
       <c r="A1037" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B1037" t="s">
         <v>406</v>
@@ -60890,18 +60890,18 @@
         <v>0</v>
       </c>
       <c r="K1037">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1037">
         <v>0</v>
       </c>
       <c r="M1037">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1038" spans="1:13">
       <c r="A1038" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B1038" t="s">
         <v>406</v>
@@ -60910,7 +60910,7 @@
         <v>1</v>
       </c>
       <c r="D1038">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1038">
         <v>0</v>
@@ -60919,7 +60919,7 @@
         <v>0</v>
       </c>
       <c r="G1038">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1038">
         <v>0</v>
@@ -60934,21 +60934,21 @@
         <v>0</v>
       </c>
       <c r="L1038">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1038">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1039" spans="1:13">
       <c r="A1039" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B1039" t="s">
         <v>406</v>
       </c>
       <c r="C1039">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1039">
         <v>0</v>
@@ -60960,7 +60960,7 @@
         <v>0</v>
       </c>
       <c r="G1039">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1039">
         <v>0</v>
@@ -60969,13 +60969,13 @@
         <v>0</v>
       </c>
       <c r="J1039">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1039">
         <v>0</v>
       </c>
       <c r="L1039">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1039">
         <v>3</v>
@@ -60983,13 +60983,13 @@
     </row>
     <row r="1040" spans="1:13">
       <c r="A1040" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B1040" t="s">
         <v>406</v>
       </c>
       <c r="C1040">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1040">
         <v>0</v>
@@ -61010,27 +61010,27 @@
         <v>0</v>
       </c>
       <c r="J1040">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1040">
         <v>0</v>
       </c>
       <c r="L1040">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1040">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1041" spans="1:13">
       <c r="A1041" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B1041" t="s">
         <v>406</v>
       </c>
       <c r="C1041">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1041">
         <v>0</v>
@@ -61057,7 +61057,7 @@
         <v>0</v>
       </c>
       <c r="L1041">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1041">
         <v>1</v>
@@ -61065,13 +61065,13 @@
     </row>
     <row r="1042" spans="1:13">
       <c r="A1042" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B1042" t="s">
         <v>406</v>
       </c>
       <c r="C1042">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1042">
         <v>0</v>
@@ -61098,7 +61098,7 @@
         <v>0</v>
       </c>
       <c r="L1042">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1042">
         <v>1</v>
@@ -61106,7 +61106,7 @@
     </row>
     <row r="1043" spans="1:13">
       <c r="A1043" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B1043" t="s">
         <v>406</v>
@@ -61139,15 +61139,15 @@
         <v>0</v>
       </c>
       <c r="L1043">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M1043">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1044" spans="1:13">
       <c r="A1044" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B1044" t="s">
         <v>406</v>
@@ -61180,15 +61180,15 @@
         <v>0</v>
       </c>
       <c r="L1044">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M1044">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1045" spans="1:13">
       <c r="A1045" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B1045" t="s">
         <v>406</v>
@@ -61200,7 +61200,7 @@
         <v>0</v>
       </c>
       <c r="E1045">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F1045">
         <v>0</v>
@@ -61221,15 +61221,15 @@
         <v>0</v>
       </c>
       <c r="L1045">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1045">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1046" spans="1:13">
       <c r="A1046" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B1046" t="s">
         <v>406</v>
@@ -61241,7 +61241,7 @@
         <v>0</v>
       </c>
       <c r="E1046">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1046">
         <v>0</v>
@@ -61256,7 +61256,7 @@
         <v>0</v>
       </c>
       <c r="J1046">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1046">
         <v>0</v>
@@ -61265,21 +61265,21 @@
         <v>0</v>
       </c>
       <c r="M1046">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1047" spans="1:13">
       <c r="A1047" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B1047" t="s">
         <v>406</v>
       </c>
       <c r="C1047">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1047">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1047">
         <v>0</v>
@@ -61297,7 +61297,7 @@
         <v>0</v>
       </c>
       <c r="J1047">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1047">
         <v>0</v>
@@ -61306,27 +61306,27 @@
         <v>0</v>
       </c>
       <c r="M1047">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1048" spans="1:13">
       <c r="A1048" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B1048" t="s">
         <v>406</v>
       </c>
       <c r="C1048">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1048">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1048">
         <v>0</v>
       </c>
       <c r="F1048">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1048">
         <v>0</v>
@@ -61341,7 +61341,7 @@
         <v>0</v>
       </c>
       <c r="K1048">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1048">
         <v>0</v>
@@ -61352,13 +61352,13 @@
     </row>
     <row r="1049" spans="1:13">
       <c r="A1049" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B1049" t="s">
         <v>406</v>
       </c>
       <c r="C1049">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1049">
         <v>0</v>
@@ -61367,7 +61367,7 @@
         <v>0</v>
       </c>
       <c r="F1049">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1049">
         <v>0</v>
@@ -61382,18 +61382,18 @@
         <v>0</v>
       </c>
       <c r="K1049">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1049">
         <v>0</v>
       </c>
       <c r="M1049">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1050" spans="1:13">
       <c r="A1050" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B1050" t="s">
         <v>406</v>
@@ -61402,7 +61402,7 @@
         <v>1</v>
       </c>
       <c r="D1050">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1050">
         <v>0</v>
@@ -61426,27 +61426,27 @@
         <v>0</v>
       </c>
       <c r="L1050">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1050">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1051" spans="1:13">
       <c r="A1051" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B1051" t="s">
         <v>406</v>
       </c>
       <c r="C1051">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1051">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1051">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1051">
         <v>0</v>
@@ -61467,27 +61467,27 @@
         <v>0</v>
       </c>
       <c r="L1051">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1051">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1052" spans="1:13">
       <c r="A1052" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B1052" t="s">
         <v>406</v>
       </c>
       <c r="C1052">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1052">
         <v>0</v>
       </c>
       <c r="E1052">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1052">
         <v>0</v>
@@ -61502,21 +61502,21 @@
         <v>0</v>
       </c>
       <c r="J1052">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1052">
         <v>0</v>
       </c>
       <c r="L1052">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1052">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1053" spans="1:13">
       <c r="A1053" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B1053" t="s">
         <v>406</v>
@@ -61543,27 +61543,27 @@
         <v>0</v>
       </c>
       <c r="J1053">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1053">
         <v>0</v>
       </c>
       <c r="L1053">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1053">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1054" spans="1:13">
       <c r="A1054" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="B1054" t="s">
         <v>406</v>
       </c>
       <c r="C1054">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1054">
         <v>0</v>
@@ -61590,7 +61590,7 @@
         <v>0</v>
       </c>
       <c r="L1054">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1054">
         <v>1</v>
@@ -61598,7 +61598,7 @@
     </row>
     <row r="1055" spans="1:13">
       <c r="A1055" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B1055" t="s">
         <v>406</v>
@@ -61639,7 +61639,7 @@
     </row>
     <row r="1056" spans="1:13">
       <c r="A1056" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B1056" t="s">
         <v>406</v>
@@ -61680,10 +61680,10 @@
     </row>
     <row r="1057" spans="1:13">
       <c r="A1057" t="s">
-        <v>342</v>
+        <v>391</v>
       </c>
       <c r="B1057" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C1057">
         <v>0</v>
@@ -61707,27 +61707,27 @@
         <v>0</v>
       </c>
       <c r="J1057">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1057">
         <v>0</v>
       </c>
       <c r="L1057">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M1057">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1058" spans="1:13">
       <c r="A1058" t="s">
-        <v>343</v>
+        <v>393</v>
       </c>
       <c r="B1058" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C1058">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D1058">
         <v>0</v>
@@ -61754,15 +61754,15 @@
         <v>0</v>
       </c>
       <c r="L1058">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M1058">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1059" spans="1:13">
       <c r="A1059" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="B1059" t="s">
         <v>407</v>
@@ -61771,7 +61771,7 @@
         <v>0</v>
       </c>
       <c r="D1059">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1059">
         <v>0</v>
@@ -61789,27 +61789,27 @@
         <v>0</v>
       </c>
       <c r="J1059">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1059">
         <v>0</v>
       </c>
       <c r="L1059">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M1059">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1060" spans="1:13">
       <c r="A1060" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="B1060" t="s">
         <v>407</v>
       </c>
       <c r="C1060">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D1060">
         <v>0</v>
@@ -61836,15 +61836,15 @@
         <v>0</v>
       </c>
       <c r="L1060">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M1060">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1061" spans="1:13">
       <c r="A1061" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B1061" t="s">
         <v>407</v>
@@ -61853,7 +61853,7 @@
         <v>0</v>
       </c>
       <c r="D1061">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1061">
         <v>0</v>
@@ -61862,7 +61862,7 @@
         <v>0</v>
       </c>
       <c r="G1061">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1061">
         <v>0</v>
@@ -61885,13 +61885,13 @@
     </row>
     <row r="1062" spans="1:13">
       <c r="A1062" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="B1062" t="s">
         <v>407</v>
       </c>
       <c r="C1062">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D1062">
         <v>0</v>
@@ -61918,21 +61918,21 @@
         <v>0</v>
       </c>
       <c r="L1062">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1062">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1063" spans="1:13">
       <c r="A1063" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B1063" t="s">
         <v>407</v>
       </c>
       <c r="C1063">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1063">
         <v>0</v>
@@ -61944,7 +61944,7 @@
         <v>0</v>
       </c>
       <c r="G1063">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1063">
         <v>0</v>
@@ -61967,19 +61967,19 @@
     </row>
     <row r="1064" spans="1:13">
       <c r="A1064" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B1064" t="s">
         <v>407</v>
       </c>
       <c r="C1064">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D1064">
         <v>0</v>
       </c>
       <c r="E1064">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1064">
         <v>0</v>
@@ -62003,18 +62003,18 @@
         <v>0</v>
       </c>
       <c r="M1064">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1065" spans="1:13">
       <c r="A1065" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B1065" t="s">
         <v>407</v>
       </c>
       <c r="C1065">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1065">
         <v>0</v>
@@ -62038,7 +62038,7 @@
         <v>0</v>
       </c>
       <c r="K1065">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1065">
         <v>0</v>
@@ -62049,7 +62049,7 @@
     </row>
     <row r="1066" spans="1:13">
       <c r="A1066" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B1066" t="s">
         <v>407</v>
@@ -62058,10 +62058,10 @@
         <v>0</v>
       </c>
       <c r="D1066">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1066">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1066">
         <v>0</v>
@@ -62082,15 +62082,15 @@
         <v>0</v>
       </c>
       <c r="L1066">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1066">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1067" spans="1:13">
       <c r="A1067" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B1067" t="s">
         <v>407</v>
@@ -62102,7 +62102,7 @@
         <v>0</v>
       </c>
       <c r="E1067">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1067">
         <v>0</v>
@@ -62120,7 +62120,7 @@
         <v>0</v>
       </c>
       <c r="K1067">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1067">
         <v>0</v>
@@ -62131,16 +62131,16 @@
     </row>
     <row r="1068" spans="1:13">
       <c r="A1068" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B1068" t="s">
         <v>407</v>
       </c>
       <c r="C1068">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1068">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1068">
         <v>0</v>
@@ -62164,15 +62164,15 @@
         <v>0</v>
       </c>
       <c r="L1068">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1068">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1069" spans="1:13">
       <c r="A1069" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B1069" t="s">
         <v>407</v>
@@ -62184,7 +62184,7 @@
         <v>0</v>
       </c>
       <c r="E1069">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1069">
         <v>0</v>
@@ -62202,7 +62202,7 @@
         <v>0</v>
       </c>
       <c r="K1069">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1069">
         <v>0</v>
@@ -62213,16 +62213,16 @@
     </row>
     <row r="1070" spans="1:13">
       <c r="A1070" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B1070" t="s">
         <v>407</v>
       </c>
       <c r="C1070">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1070">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1070">
         <v>0</v>
@@ -62254,7 +62254,7 @@
     </row>
     <row r="1071" spans="1:13">
       <c r="A1071" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B1071" t="s">
         <v>407</v>
@@ -62266,7 +62266,7 @@
         <v>0</v>
       </c>
       <c r="E1071">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1071">
         <v>0</v>
@@ -62284,7 +62284,7 @@
         <v>0</v>
       </c>
       <c r="K1071">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1071">
         <v>0</v>
@@ -62295,16 +62295,16 @@
     </row>
     <row r="1072" spans="1:13">
       <c r="A1072" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B1072" t="s">
         <v>407</v>
       </c>
       <c r="C1072">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1072">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1072">
         <v>0</v>
@@ -62336,7 +62336,7 @@
     </row>
     <row r="1073" spans="1:13">
       <c r="A1073" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B1073" t="s">
         <v>407</v>
@@ -62348,7 +62348,7 @@
         <v>0</v>
       </c>
       <c r="E1073">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1073">
         <v>0</v>
@@ -62369,7 +62369,7 @@
         <v>0</v>
       </c>
       <c r="L1073">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1073">
         <v>1</v>
@@ -62377,13 +62377,13 @@
     </row>
     <row r="1074" spans="1:13">
       <c r="A1074" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B1074" t="s">
         <v>407</v>
       </c>
       <c r="C1074">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1074">
         <v>0</v>
@@ -62395,7 +62395,7 @@
         <v>0</v>
       </c>
       <c r="G1074">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1074">
         <v>0</v>
@@ -62418,7 +62418,7 @@
     </row>
     <row r="1075" spans="1:13">
       <c r="A1075" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B1075" t="s">
         <v>407</v>
@@ -62459,7 +62459,7 @@
     </row>
     <row r="1076" spans="1:13">
       <c r="A1076" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="B1076" t="s">
         <v>407</v>
@@ -62471,13 +62471,13 @@
         <v>0</v>
       </c>
       <c r="E1076">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1076">
         <v>0</v>
       </c>
       <c r="G1076">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1076">
         <v>0</v>
@@ -62500,7 +62500,7 @@
     </row>
     <row r="1077" spans="1:13">
       <c r="A1077" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="B1077" t="s">
         <v>407</v>
@@ -62541,7 +62541,7 @@
     </row>
     <row r="1078" spans="1:13">
       <c r="A1078" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B1078" t="s">
         <v>407</v>
@@ -62553,7 +62553,7 @@
         <v>0</v>
       </c>
       <c r="E1078">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1078">
         <v>0</v>
@@ -62574,7 +62574,7 @@
         <v>0</v>
       </c>
       <c r="L1078">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1078">
         <v>1</v>
@@ -62582,7 +62582,7 @@
     </row>
     <row r="1079" spans="1:13">
       <c r="A1079" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B1079" t="s">
         <v>407</v>
@@ -62623,16 +62623,16 @@
     </row>
     <row r="1080" spans="1:13">
       <c r="A1080" t="s">
-        <v>364</v>
+        <v>392</v>
       </c>
       <c r="B1080" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C1080">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1080">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1080">
         <v>0</v>
@@ -62656,24 +62656,24 @@
         <v>0</v>
       </c>
       <c r="L1080">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1080">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1081" spans="1:13">
       <c r="A1081" t="s">
-        <v>366</v>
+        <v>393</v>
       </c>
       <c r="B1081" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C1081">
         <v>0</v>
       </c>
       <c r="D1081">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1081">
         <v>0</v>
@@ -62700,24 +62700,24 @@
         <v>1</v>
       </c>
       <c r="M1081">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1082" spans="1:13">
       <c r="A1082" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B1082" t="s">
         <v>408</v>
       </c>
       <c r="C1082">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1082">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1082">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1082">
         <v>0</v>
@@ -62741,12 +62741,12 @@
         <v>0</v>
       </c>
       <c r="M1082">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1083" spans="1:13">
       <c r="A1083" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B1083" t="s">
         <v>408</v>
@@ -62755,10 +62755,10 @@
         <v>0</v>
       </c>
       <c r="D1083">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1083">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1083">
         <v>0</v>
@@ -62776,10 +62776,10 @@
         <v>0</v>
       </c>
       <c r="K1083">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L1083">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1083">
         <v>2</v>
@@ -62787,19 +62787,19 @@
     </row>
     <row r="1084" spans="1:13">
       <c r="A1084" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B1084" t="s">
         <v>408</v>
       </c>
       <c r="C1084">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1084">
         <v>0</v>
       </c>
       <c r="E1084">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1084">
         <v>0</v>
@@ -62828,7 +62828,7 @@
     </row>
     <row r="1085" spans="1:13">
       <c r="A1085" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B1085" t="s">
         <v>408</v>
@@ -62840,7 +62840,7 @@
         <v>0</v>
       </c>
       <c r="E1085">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1085">
         <v>0</v>
@@ -62858,24 +62858,24 @@
         <v>0</v>
       </c>
       <c r="K1085">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L1085">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1085">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1086" spans="1:13">
       <c r="A1086" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B1086" t="s">
         <v>408</v>
       </c>
       <c r="C1086">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1086">
         <v>0</v>
@@ -62905,12 +62905,12 @@
         <v>0</v>
       </c>
       <c r="M1086">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1087" spans="1:13">
       <c r="A1087" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B1087" t="s">
         <v>408</v>
@@ -62919,7 +62919,7 @@
         <v>0</v>
       </c>
       <c r="D1087">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1087">
         <v>0</v>
@@ -62946,21 +62946,21 @@
         <v>1</v>
       </c>
       <c r="M1087">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1088" spans="1:13">
       <c r="A1088" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B1088" t="s">
         <v>408</v>
       </c>
       <c r="C1088">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D1088">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1088">
         <v>0</v>
@@ -62987,12 +62987,12 @@
         <v>0</v>
       </c>
       <c r="M1088">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1089" spans="1:13">
       <c r="A1089" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B1089" t="s">
         <v>408</v>
@@ -63001,7 +63001,7 @@
         <v>0</v>
       </c>
       <c r="D1089">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1089">
         <v>0</v>
@@ -63010,7 +63010,7 @@
         <v>0</v>
       </c>
       <c r="G1089">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1089">
         <v>0</v>
@@ -63025,24 +63025,24 @@
         <v>0</v>
       </c>
       <c r="L1089">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1089">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1090" spans="1:13">
       <c r="A1090" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B1090" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C1090">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1090">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E1090">
         <v>0</v>
@@ -63066,18 +63066,18 @@
         <v>0</v>
       </c>
       <c r="L1090">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1090">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1091" spans="1:13">
       <c r="A1091" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B1091" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C1091">
         <v>0</v>
@@ -63092,7 +63092,7 @@
         <v>0</v>
       </c>
       <c r="G1091">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1091">
         <v>0</v>
@@ -63107,7 +63107,7 @@
         <v>0</v>
       </c>
       <c r="L1091">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1091">
         <v>1</v>
@@ -63115,16 +63115,16 @@
     </row>
     <row r="1092" spans="1:13">
       <c r="A1092" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B1092" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C1092">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1092">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E1092">
         <v>0</v>
@@ -63148,15 +63148,15 @@
         <v>0</v>
       </c>
       <c r="L1092">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1092">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1093" spans="1:13">
       <c r="A1093" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="B1093" t="s">
         <v>409</v>
@@ -63165,7 +63165,7 @@
         <v>1</v>
       </c>
       <c r="D1093">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E1093">
         <v>0</v>
@@ -63189,15 +63189,15 @@
         <v>0</v>
       </c>
       <c r="L1093">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1093">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1094" spans="1:13">
       <c r="A1094" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B1094" t="s">
         <v>409</v>
@@ -63238,7 +63238,7 @@
     </row>
     <row r="1095" spans="1:13">
       <c r="A1095" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="B1095" t="s">
         <v>409</v>
@@ -63247,7 +63247,7 @@
         <v>1</v>
       </c>
       <c r="D1095">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E1095">
         <v>0</v>
@@ -63274,21 +63274,21 @@
         <v>0</v>
       </c>
       <c r="M1095">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1096" spans="1:13">
       <c r="A1096" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B1096" t="s">
         <v>409</v>
       </c>
       <c r="C1096">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1096">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E1096">
         <v>0</v>
@@ -63315,15 +63315,15 @@
         <v>0</v>
       </c>
       <c r="M1096">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1097" spans="1:13">
       <c r="A1097" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="B1097" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C1097">
         <v>0</v>
@@ -63338,7 +63338,7 @@
         <v>0</v>
       </c>
       <c r="G1097">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1097">
         <v>0</v>
@@ -63347,27 +63347,27 @@
         <v>0</v>
       </c>
       <c r="J1097">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1097">
         <v>0</v>
       </c>
       <c r="L1097">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1097">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1098" spans="1:13">
       <c r="A1098" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="B1098" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C1098">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D1098">
         <v>0</v>
@@ -63394,7 +63394,7 @@
         <v>0</v>
       </c>
       <c r="L1098">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1098">
         <v>1</v>
@@ -63402,16 +63402,16 @@
     </row>
     <row r="1099" spans="1:13">
       <c r="A1099" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="B1099" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C1099">
         <v>0</v>
       </c>
       <c r="D1099">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E1099">
         <v>0</v>
@@ -63429,27 +63429,27 @@
         <v>0</v>
       </c>
       <c r="J1099">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1099">
         <v>0</v>
       </c>
       <c r="L1099">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M1099">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1100" spans="1:13">
       <c r="A1100" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B1100" t="s">
         <v>410</v>
       </c>
       <c r="C1100">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D1100">
         <v>0</v>
@@ -63461,7 +63461,7 @@
         <v>0</v>
       </c>
       <c r="G1100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1100">
         <v>0</v>
@@ -63470,7 +63470,7 @@
         <v>0</v>
       </c>
       <c r="J1100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K1100">
         <v>0</v>
@@ -63484,13 +63484,13 @@
     </row>
     <row r="1101" spans="1:13">
       <c r="A1101" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B1101" t="s">
         <v>410</v>
       </c>
       <c r="C1101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D1101">
         <v>0</v>
@@ -63517,9 +63517,132 @@
         <v>0</v>
       </c>
       <c r="L1101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M1101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:13">
+      <c r="A1102" t="s">
+        <v>376</v>
+      </c>
+      <c r="B1102" t="s">
+        <v>410</v>
+      </c>
+      <c r="C1102">
+        <v>0</v>
+      </c>
+      <c r="D1102">
+        <v>0</v>
+      </c>
+      <c r="E1102">
+        <v>0</v>
+      </c>
+      <c r="F1102">
+        <v>0</v>
+      </c>
+      <c r="G1102">
+        <v>0</v>
+      </c>
+      <c r="H1102">
+        <v>0</v>
+      </c>
+      <c r="I1102">
+        <v>0</v>
+      </c>
+      <c r="J1102">
+        <v>0</v>
+      </c>
+      <c r="K1102">
+        <v>0</v>
+      </c>
+      <c r="L1102">
+        <v>1</v>
+      </c>
+      <c r="M1102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:13">
+      <c r="A1103" t="s">
+        <v>377</v>
+      </c>
+      <c r="B1103" t="s">
+        <v>410</v>
+      </c>
+      <c r="C1103">
+        <v>2</v>
+      </c>
+      <c r="D1103">
+        <v>0</v>
+      </c>
+      <c r="E1103">
+        <v>0</v>
+      </c>
+      <c r="F1103">
+        <v>0</v>
+      </c>
+      <c r="G1103">
+        <v>0</v>
+      </c>
+      <c r="H1103">
+        <v>0</v>
+      </c>
+      <c r="I1103">
+        <v>0</v>
+      </c>
+      <c r="J1103">
+        <v>0</v>
+      </c>
+      <c r="K1103">
+        <v>0</v>
+      </c>
+      <c r="L1103">
+        <v>0</v>
+      </c>
+      <c r="M1103">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:13">
+      <c r="A1104" t="s">
+        <v>384</v>
+      </c>
+      <c r="B1104" t="s">
+        <v>410</v>
+      </c>
+      <c r="C1104">
+        <v>1</v>
+      </c>
+      <c r="D1104">
+        <v>0</v>
+      </c>
+      <c r="E1104">
+        <v>0</v>
+      </c>
+      <c r="F1104">
+        <v>0</v>
+      </c>
+      <c r="G1104">
+        <v>0</v>
+      </c>
+      <c r="H1104">
+        <v>0</v>
+      </c>
+      <c r="I1104">
+        <v>0</v>
+      </c>
+      <c r="J1104">
+        <v>0</v>
+      </c>
+      <c r="K1104">
+        <v>0</v>
+      </c>
+      <c r="L1104">
+        <v>0</v>
+      </c>
+      <c r="M1104">
         <v>1</v>
       </c>
     </row>
